--- a/database/event/2112/event_2112_evp_summary.xlsx
+++ b/database/event/2112/event_2112_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0822</v>
+        <v>6.9688</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6503</v>
+        <v>1.8909</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0357</v>
+        <v>2.3325</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0822</v>
+        <v>6.9688</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7294</v>
+        <v>3.6159</v>
       </c>
       <c r="G2" t="n">
         <v>3.3529</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7294</v>
+        <v>3.6159</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2122</v>
+        <v>2.9308</v>
       </c>
       <c r="J2" t="n">
         <v>3.3529</v>
@@ -529,7 +529,7 @@
         <v>129</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5651</v>
+        <v>6.2837</v>
       </c>
       <c r="N2" t="n">
         <v>179</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0277</v>
+        <v>6.4236</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6355</v>
+        <v>1.743</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0137</v>
+        <v>2.1153</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0277</v>
+        <v>6.4236</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6003</v>
+        <v>1.9962</v>
       </c>
       <c r="G3" t="n">
         <v>4.4274</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6003</v>
+        <v>1.9962</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2971</v>
+        <v>1.618</v>
       </c>
       <c r="J3" t="n">
         <v>4.4274</v>
@@ -575,7 +575,7 @@
         <v>129</v>
       </c>
       <c r="M3" t="n">
-        <v>5.724499999999999</v>
+        <v>6.0454</v>
       </c>
       <c r="N3" t="n">
         <v>179</v>
@@ -594,7 +594,7 @@
         <v>1.517</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8372</v>
+        <v>1.7835</v>
       </c>
       <c r="E4" t="n">
         <v>5.5908</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1381</v>
+        <v>4.7528</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1228</v>
+        <v>1.2896</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2503</v>
+        <v>1.4496</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1381</v>
+        <v>4.7528</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4081</v>
+        <v>3.0228</v>
       </c>
       <c r="G5" t="n">
         <v>1.73</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4081</v>
+        <v>3.0228</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9519</v>
+        <v>2.4501</v>
       </c>
       <c r="J5" t="n">
         <v>1.73</v>
@@ -667,7 +667,7 @@
         <v>127</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6819</v>
+        <v>4.180099999999999</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -686,7 +686,7 @@
         <v>1.042</v>
       </c>
       <c r="D6" t="n">
-        <v>1.13</v>
+        <v>1.0861</v>
       </c>
       <c r="E6" t="n">
         <v>3.8403</v>
@@ -732,7 +732,7 @@
         <v>1.0275</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1084</v>
+        <v>1.0647</v>
       </c>
       <c r="E7" t="n">
         <v>3.7867</v>
@@ -778,7 +778,7 @@
         <v>1.0231</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1018</v>
+        <v>1.0582</v>
       </c>
       <c r="E8" t="n">
         <v>3.7704</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3526</v>
+        <v>3.5968</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9097</v>
+        <v>0.9759</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9891</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3526</v>
+        <v>3.5968</v>
       </c>
       <c r="F9" t="n">
-        <v>4.3526</v>
+        <v>3.6929</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>-0.0961</v>
       </c>
       <c r="H9" t="n">
-        <v>4.951</v>
+        <v>3.6929</v>
       </c>
       <c r="I9" t="n">
-        <v>4.013</v>
+        <v>2.9932</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>-0.0961</v>
       </c>
       <c r="K9" t="n">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="L9" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="M9" t="n">
-        <v>3.013</v>
+        <v>2.8971</v>
       </c>
       <c r="N9" t="n">
-        <v>273</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.166</v>
+        <v>3.3526</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8591</v>
+        <v>0.9097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8576</v>
+        <v>0.8918</v>
       </c>
       <c r="E10" t="n">
-        <v>3.166</v>
+        <v>3.3526</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7965</v>
+        <v>4.3526</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3695</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7965</v>
+        <v>4.951</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4561</v>
+        <v>4.013</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3695</v>
+        <v>-1</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="L10" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8256</v>
+        <v>3.013</v>
       </c>
       <c r="N10" t="n">
-        <v>171</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0142</v>
+        <v>3.2781</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8179</v>
+        <v>0.8895</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7963</v>
+        <v>0.8621</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0142</v>
+        <v>3.2781</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6117</v>
+        <v>1.9086</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4025</v>
+        <v>1.3695</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6117</v>
+        <v>1.9086</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1169</v>
+        <v>1.547</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4025</v>
+        <v>1.3695</v>
       </c>
       <c r="K11" t="n">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5194</v>
+        <v>2.9165</v>
       </c>
       <c r="N11" t="n">
-        <v>273</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7397</v>
+        <v>3.0142</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8179</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6854</v>
+        <v>0.7569</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7397</v>
+        <v>3.0142</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9164</v>
+        <v>2.6117</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8233</v>
+        <v>0.4025</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9164</v>
+        <v>2.6117</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7428</v>
+        <v>2.1169</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8233</v>
+        <v>0.4025</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="L12" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5661</v>
+        <v>2.5194</v>
       </c>
       <c r="N12" t="n">
-        <v>179</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6898</v>
+        <v>2.8307</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7298</v>
+        <v>0.7681</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6653</v>
+        <v>0.6838</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6898</v>
+        <v>2.8307</v>
       </c>
       <c r="F13" t="n">
-        <v>0.777</v>
+        <v>0.9179</v>
       </c>
       <c r="G13" t="n">
         <v>1.9128</v>
       </c>
       <c r="H13" t="n">
-        <v>0.777</v>
+        <v>0.9179</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6298</v>
+        <v>0.744</v>
       </c>
       <c r="J13" t="n">
         <v>1.9128</v>
@@ -1035,7 +1035,7 @@
         <v>129</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5426</v>
+        <v>2.6568</v>
       </c>
       <c r="N13" t="n">
         <v>179</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6753</v>
+        <v>2.7397</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7259</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6594</v>
+        <v>0.6476</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6753</v>
+        <v>2.7397</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7714</v>
+        <v>0.9164</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0961</v>
+        <v>1.8233</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7714</v>
+        <v>0.9164</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2463</v>
+        <v>0.7428</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0961</v>
+        <v>1.8233</v>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1502</v>
+        <v>2.5661</v>
       </c>
       <c r="N14" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15">
@@ -1100,7 +1100,7 @@
         <v>0.5837</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4476</v>
+        <v>0.4131</v>
       </c>
       <c r="E15" t="n">
         <v>2.1511</v>
@@ -1146,7 +1146,7 @@
         <v>0.573</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4317</v>
+        <v>0.3974</v>
       </c>
       <c r="E16" t="n">
         <v>2.1116</v>
@@ -1192,7 +1192,7 @@
         <v>0.4742</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2847</v>
+        <v>0.2524</v>
       </c>
       <c r="E17" t="n">
         <v>1.7478</v>
@@ -1238,7 +1238,7 @@
         <v>0.2892</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0092</v>
+        <v>-0.0193</v>
       </c>
       <c r="E18" t="n">
         <v>1.0659</v>
@@ -1284,7 +1284,7 @@
         <v>0.1938</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1328</v>
+        <v>-0.1593</v>
       </c>
       <c r="E19" t="n">
         <v>0.7144</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1711</v>
+        <v>0.1788</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1666</v>
+        <v>-0.1813</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6307</v>
+        <v>0.6591</v>
       </c>
       <c r="N20" t="n">
         <v>96</v>
@@ -1366,231 +1366,231 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1644</v>
+        <v>0.1711</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1766</v>
+        <v>-0.1926</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6058</v>
+        <v>0.6307</v>
       </c>
       <c r="N21" t="n">
-        <v>165</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="C22" t="n">
-        <v>0.152</v>
+        <v>0.1644</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1951</v>
+        <v>-0.2026</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5601</v>
+        <v>0.6058</v>
       </c>
       <c r="N22" t="n">
-        <v>81</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1038</v>
+        <v>0.152</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2668</v>
+        <v>-0.2208</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3826</v>
+        <v>0.5601</v>
       </c>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3271</v>
+        <v>0.5</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0888</v>
+        <v>0.1357</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2892</v>
+        <v>-0.2447</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3271</v>
+        <v>0.5</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0265</v>
+        <v>0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6994</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0265</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.832</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6994</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="L24" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1325999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="N24" t="n">
-        <v>179</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2823</v>
+        <v>0.4033</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0766</v>
+        <v>0.1094</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3073</v>
+        <v>-0.2832</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2823</v>
+        <v>0.4033</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2823</v>
+        <v>1.1027</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.6994</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2823</v>
+        <v>1.1027</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2823</v>
+        <v>0.8938</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.6994</v>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2823</v>
+        <v>0.1944</v>
       </c>
       <c r="N25" t="n">
-        <v>90</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0668</v>
+        <v>0.3402</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0181</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3944</v>
+        <v>-0.3084</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0668</v>
+        <v>0.3402</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5174</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-0.4506</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5174</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4194</v>
+        <v>0.641</v>
       </c>
       <c r="J26" t="n">
         <v>-0.4506</v>
@@ -1633,7 +1633,7 @@
         <v>127</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03120000000000001</v>
+        <v>0.1904</v>
       </c>
       <c r="N26" t="n">
         <v>171</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0137</v>
+        <v>0.0766</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4417</v>
+        <v>-0.3314</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0504</v>
+        <v>0.2823</v>
       </c>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0137</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5148</v>
+        <v>-0.464</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2313</v>
+        <v>-0.0504</v>
       </c>
       <c r="N28" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.2102</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7343</v>
+        <v>-0.7526</v>
       </c>
       <c r="E29" t="n">
         <v>-0.7747000000000001</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2118</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7367</v>
+        <v>-0.7549</v>
       </c>
       <c r="E30" t="n">
         <v>-0.7805</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2171</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2201</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7491</v>
+        <v>-0.7671</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8113</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2267</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7589</v>
+        <v>-0.7768</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8356</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3085</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8807</v>
+        <v>-0.8969</v>
       </c>
       <c r="E34" t="n">
         <v>-1.137</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3219</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.9166</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1865</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3696</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9716</v>
+        <v>-0.9866</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3621</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4017</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0194</v>
+        <v>-1.0337</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4804</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4714</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1232</v>
+        <v>-1.136</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7372</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4721</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1242</v>
+        <v>-1.137</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7398</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5296999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.21</v>
+        <v>-1.2217</v>
       </c>
       <c r="E40" t="n">
         <v>-1.9522</v>
@@ -2296,7 +2296,7 @@
         <v>-0.737</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5186</v>
+        <v>-1.526</v>
       </c>
       <c r="E41" t="n">
         <v>-2.716</v>

--- a/database/event/2112/event_2112_evp_summary.xlsx
+++ b/database/event/2112/event_2112_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9688</v>
+        <v>6.2919</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8909</v>
+        <v>1.7072</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3325</v>
+        <v>2.2025</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9688</v>
+        <v>6.2919</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6159</v>
+        <v>2.4124</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3529</v>
+        <v>3.8795</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6159</v>
+        <v>3.0135</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9308</v>
+        <v>1.5669</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3529</v>
+        <v>3.8795</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>129</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2837</v>
+        <v>5.446400000000001</v>
       </c>
       <c r="N2" t="n">
         <v>179</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4236</v>
+        <v>5.8752</v>
       </c>
       <c r="C3" t="n">
-        <v>1.743</v>
+        <v>1.5942</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1153</v>
+        <v>2.0143</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4236</v>
+        <v>5.8752</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9962</v>
+        <v>2.9851</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4274</v>
+        <v>2.8901</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9962</v>
+        <v>5.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>1.618</v>
+        <v>2.616</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4274</v>
+        <v>2.8901</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -575,7 +575,7 @@
         <v>129</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0454</v>
+        <v>5.5061</v>
       </c>
       <c r="N3" t="n">
         <v>179</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5908</v>
+        <v>4.9829</v>
       </c>
       <c r="C4" t="n">
-        <v>1.517</v>
+        <v>1.352</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7835</v>
+        <v>1.6115</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5908</v>
+        <v>4.9829</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0442</v>
+        <v>3.6977</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5466</v>
+        <v>1.2852</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0442</v>
+        <v>7.5422</v>
       </c>
       <c r="I4" t="n">
-        <v>3.278</v>
+        <v>3.9216</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5466</v>
+        <v>1.2852</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8246</v>
+        <v>5.2068</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7528</v>
+        <v>4.4172</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2896</v>
+        <v>1.1986</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4496</v>
+        <v>1.3561</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7528</v>
+        <v>4.4172</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0228</v>
+        <v>2.8031</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>1.6141</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0228</v>
+        <v>4.3901</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4501</v>
+        <v>2.2826</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.6141</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>127</v>
       </c>
       <c r="M5" t="n">
-        <v>4.180099999999999</v>
+        <v>3.8967</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8403</v>
+        <v>3.6952</v>
       </c>
       <c r="C6" t="n">
-        <v>1.042</v>
+        <v>1.0026</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0861</v>
+        <v>1.0302</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8403</v>
+        <v>3.6952</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2308</v>
+        <v>3.8875</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3905</v>
+        <v>-0.1923</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4611</v>
+        <v>8.210900000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6159</v>
+        <v>4.2693</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3905</v>
+        <v>-0.1923</v>
       </c>
       <c r="K6" t="n">
         <v>142</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2254</v>
+        <v>4.077</v>
       </c>
       <c r="N6" t="n">
         <v>221</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7867</v>
+        <v>3.5567</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0275</v>
+        <v>0.9651</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0647</v>
+        <v>0.9677</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7867</v>
+        <v>3.5567</v>
       </c>
       <c r="F7" t="n">
-        <v>4.313</v>
+        <v>3.8095</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5263</v>
+        <v>-0.2528</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7919</v>
+        <v>7.9359</v>
       </c>
       <c r="I7" t="n">
-        <v>3.884</v>
+        <v>4.1263</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5263</v>
+        <v>-0.2528</v>
       </c>
       <c r="K7" t="n">
         <v>142</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3577</v>
+        <v>3.873499999999999</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,127 +768,127 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7704</v>
+        <v>3.5348</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0231</v>
+        <v>0.9591</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0582</v>
+        <v>0.9578</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7704</v>
+        <v>3.5348</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0537</v>
+        <v>2.4873</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2833</v>
+        <v>1.0475</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0537</v>
+        <v>3.2772</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2857</v>
+        <v>1.704</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2833</v>
+        <v>1.0475</v>
       </c>
       <c r="K8" t="n">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0024</v>
+        <v>2.7515</v>
       </c>
       <c r="N8" t="n">
-        <v>273</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5968</v>
+        <v>3.3463</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9759</v>
+        <v>0.908</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9891</v>
+        <v>0.8727</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5968</v>
+        <v>3.3463</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6929</v>
+        <v>1.7452</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0961</v>
+        <v>1.6011</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6929</v>
+        <v>1.7452</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9932</v>
+        <v>0.9074</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0961</v>
+        <v>1.6011</v>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8971</v>
+        <v>2.5085</v>
       </c>
       <c r="N9" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3526</v>
+        <v>3.3258</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9097</v>
+        <v>0.9024</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8918</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3526</v>
+        <v>3.3258</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3526</v>
+        <v>2.9015</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0.4243</v>
       </c>
       <c r="H10" t="n">
-        <v>4.951</v>
+        <v>4.7368</v>
       </c>
       <c r="I10" t="n">
-        <v>4.013</v>
+        <v>2.4629</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>0.4243</v>
       </c>
       <c r="K10" t="n">
         <v>196</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.013</v>
+        <v>2.8872</v>
       </c>
       <c r="N10" t="n">
         <v>273</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2781</v>
+        <v>3.2762</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8895</v>
+        <v>0.889</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8621</v>
+        <v>0.841</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2781</v>
+        <v>3.2762</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9086</v>
+        <v>3.0076</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3695</v>
+        <v>0.2686</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9086</v>
+        <v>5.1105</v>
       </c>
       <c r="I11" t="n">
-        <v>1.547</v>
+        <v>2.6572</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3695</v>
+        <v>0.2686</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>127</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9165</v>
+        <v>2.9258</v>
       </c>
       <c r="N11" t="n">
         <v>171</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0142</v>
+        <v>3.269</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8179</v>
+        <v>0.887</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7569</v>
+        <v>0.8378</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0142</v>
+        <v>3.269</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6117</v>
+        <v>3.4212</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4025</v>
+        <v>-0.1522</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6117</v>
+        <v>6.5677</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1169</v>
+        <v>3.4149</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4025</v>
+        <v>-0.1522</v>
       </c>
       <c r="K12" t="n">
         <v>196</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5194</v>
+        <v>3.2627</v>
       </c>
       <c r="N12" t="n">
         <v>273</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8307</v>
+        <v>3.2304</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7681</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6838</v>
+        <v>0.8204</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8307</v>
+        <v>3.2304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9179</v>
+        <v>4.0573</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9128</v>
+        <v>-0.8269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9179</v>
+        <v>8.808999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.744</v>
+        <v>4.5803</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9128</v>
+        <v>-0.8269</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="L13" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6568</v>
+        <v>3.7534</v>
       </c>
       <c r="N13" t="n">
-        <v>179</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7397</v>
+        <v>3.1731</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6476</v>
+        <v>0.7945</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7397</v>
+        <v>3.1731</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9164</v>
+        <v>1.633</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8233</v>
+        <v>1.5401</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9164</v>
+        <v>1.633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7428</v>
+        <v>0.8491</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8233</v>
+        <v>1.5401</v>
       </c>
       <c r="K14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>129</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5661</v>
+        <v>2.3892</v>
       </c>
       <c r="N14" t="n">
         <v>179</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1511</v>
+        <v>2.5202</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5837</v>
+        <v>0.6838</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4131</v>
+        <v>0.4997</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1511</v>
+        <v>2.5202</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8228</v>
+        <v>2.9003</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6717</v>
+        <v>-0.3801</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8228</v>
+        <v>4.7325</v>
       </c>
       <c r="I15" t="n">
-        <v>2.288</v>
+        <v>2.4607</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6717</v>
+        <v>-0.3801</v>
       </c>
       <c r="K15" t="n">
         <v>142</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6163</v>
+        <v>2.0806</v>
       </c>
       <c r="N15" t="n">
         <v>221</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1116</v>
+        <v>2.2459</v>
       </c>
       <c r="C16" t="n">
-        <v>0.573</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3974</v>
+        <v>0.3759</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1116</v>
+        <v>2.2459</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1116</v>
+        <v>3.032</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>-0.7861</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1116</v>
+        <v>5.1964</v>
       </c>
       <c r="I16" t="n">
-        <v>2.522</v>
+        <v>2.7019</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>-0.7861</v>
       </c>
       <c r="K16" t="n">
         <v>196</v>
@@ -1173,7 +1173,7 @@
         <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>1.522</v>
+        <v>1.9158</v>
       </c>
       <c r="N16" t="n">
         <v>273</v>
@@ -1182,354 +1182,354 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7478</v>
+        <v>1.5954</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4742</v>
+        <v>0.4329</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2524</v>
+        <v>0.0822</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7478</v>
+        <v>1.5954</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4683</v>
+        <v>2.0669</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2162</v>
+        <v>-0.4715</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4683</v>
+        <v>2.0669</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3796</v>
+        <v>1.0747</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2162</v>
+        <v>-0.4715</v>
       </c>
       <c r="K17" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L17" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8366</v>
+        <v>0.6032</v>
       </c>
       <c r="N17" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>spaze</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0659</v>
+        <v>1.2971</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2892</v>
+        <v>0.352</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0193</v>
+        <v>-0.0524</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0659</v>
+        <v>1.2971</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0659</v>
+        <v>1.2907</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0659</v>
+        <v>1.2907</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0659</v>
+        <v>0.6711</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="K18" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0659</v>
+        <v>0.6775</v>
       </c>
       <c r="N18" t="n">
-        <v>81</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>spaze</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1938</v>
+        <v>0.3261</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1593</v>
+        <v>-0.0955</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7144</v>
+        <v>1.2017</v>
       </c>
       <c r="N19" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6591</v>
+        <v>1.1942</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1788</v>
+        <v>0.324</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1813</v>
+        <v>-0.0989</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6591</v>
+        <v>1.1942</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6591</v>
+        <v>-0.441</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6591</v>
+        <v>-0.441</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6591</v>
+        <v>-0.2293</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="K20" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6591</v>
+        <v>1.4059</v>
       </c>
       <c r="N20" t="n">
-        <v>96</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1711</v>
+        <v>0.251</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1926</v>
+        <v>-0.2203</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6307</v>
+        <v>0.9252</v>
       </c>
       <c r="N21" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1644</v>
+        <v>0.2066</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2026</v>
+        <v>-0.2943</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6058</v>
+        <v>0.7614</v>
       </c>
       <c r="N22" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="C23" t="n">
-        <v>0.152</v>
+        <v>0.2039</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2208</v>
+        <v>-0.2987</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5601</v>
+        <v>0.7516</v>
       </c>
       <c r="N23" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1357</v>
+        <v>0.1864</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2447</v>
+        <v>-0.3279</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>96</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4033</v>
+        <v>0.6665</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1094</v>
+        <v>0.1808</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2832</v>
+        <v>-0.3371</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4033</v>
+        <v>0.6665</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1027</v>
+        <v>0.6665</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6994</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1027</v>
+        <v>0.6665</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8938</v>
+        <v>0.6665</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6994</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="L25" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1944</v>
+        <v>0.6665</v>
       </c>
       <c r="N25" t="n">
-        <v>179</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3402</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1508</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3084</v>
+        <v>-0.3871</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3402</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4506</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.641</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4506</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="L26" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1904</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0766</v>
+        <v>0.115</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3314</v>
+        <v>-0.4467</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2823</v>
+        <v>0.4238</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0137</v>
+        <v>0.0224</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.464</v>
+        <v>-0.6008</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0504</v>
+        <v>0.0825</v>
       </c>
       <c r="N28" t="n">
         <v>81</v>
@@ -1734,78 +1734,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.3575</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2102</v>
+        <v>-0.097</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7526</v>
+        <v>-0.7994</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.3575</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1627</v>
+        <v>-0.3575</v>
       </c>
       <c r="G29" t="n">
-        <v>0.388</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1627</v>
+        <v>-0.3575</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9424</v>
+        <v>-0.3575</v>
       </c>
       <c r="J29" t="n">
-        <v>0.388</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5544</v>
+        <v>-0.3575</v>
       </c>
       <c r="N29" t="n">
-        <v>273</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2118</v>
+        <v>-0.1085</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7549</v>
+        <v>-0.8186</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4</v>
       </c>
       <c r="N30" t="n">
         <v>165</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2171</v>
+        <v>-0.1361</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.8645</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8</v>
+        <v>-0.5017</v>
       </c>
       <c r="N31" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2201</v>
+        <v>-0.1517</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7671</v>
+        <v>-0.8904</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8113</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8356</v>
+        <v>-0.6956</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2267</v>
+        <v>-0.1887</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7768</v>
+        <v>-0.952</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8356</v>
+        <v>-0.6956</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8356</v>
+        <v>-0.9318</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.2362</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8356</v>
+        <v>-0.9318</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8356</v>
+        <v>-0.4845</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.2362</v>
       </c>
       <c r="K33" t="n">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8356</v>
+        <v>-0.2483</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3085</v>
+        <v>-0.1959</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8969</v>
+        <v>-0.9639</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.137</v>
+        <v>-0.7218</v>
       </c>
       <c r="N34" t="n">
         <v>165</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3219</v>
+        <v>-0.2041</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9166</v>
+        <v>-0.9776</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1865</v>
+        <v>-0.7523</v>
       </c>
       <c r="N35" t="n">
         <v>81</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3696</v>
+        <v>-0.251</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9866</v>
+        <v>-1.0556</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3621</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>90</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4017</v>
+        <v>-0.26</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0337</v>
+        <v>-1.0706</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4804</v>
+        <v>-0.9583</v>
       </c>
       <c r="N37" t="n">
         <v>81</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7372</v>
+        <v>-0.995</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4714</v>
+        <v>-0.27</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.136</v>
+        <v>-1.0872</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7372</v>
+        <v>-0.995</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7372</v>
+        <v>-0.2679</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.7271</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7372</v>
+        <v>-0.2679</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7372</v>
+        <v>-0.1393</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.7271</v>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7372</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>90</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4721</v>
+        <v>-0.3463</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.137</v>
+        <v>-1.2141</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7398</v>
+        <v>-1.2761</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9522</v>
+        <v>-1.4263</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.387</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2217</v>
+        <v>-1.2819</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9522</v>
+        <v>-1.4263</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9522</v>
+        <v>-1.4263</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9522</v>
+        <v>-1.4263</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7718</v>
+        <v>-1.4263</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="L40" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7718</v>
+        <v>-1.4263</v>
       </c>
       <c r="N40" t="n">
-        <v>221</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.737</v>
+        <v>-0.6899</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.526</v>
+        <v>-1.7859</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.716</v>
+        <v>-2.5427</v>
       </c>
       <c r="N41" t="n">
         <v>96</v>
@@ -2429,10 +2429,10 @@
         <v>1.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.412</v>
+        <v>0.4649</v>
       </c>
       <c r="J2" t="n">
-        <v>10.3</v>
+        <v>11.6225</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0514</v>
+        <v>-0.0646</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.285</v>
+        <v>-1.615</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3815</v>
+        <v>-0.2543</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.5375</v>
+        <v>-6.3575</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5833</v>
+        <v>-0.3872</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.5825</v>
+        <v>-9.68</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.55</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.4523</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.8475</v>
+        <v>-11.3075</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5825</v>
+        <v>1.3793</v>
       </c>
       <c r="J7" t="n">
-        <v>39.5625</v>
+        <v>34.4825</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7892</v>
+        <v>0.8051</v>
       </c>
       <c r="J8" t="n">
-        <v>19.73</v>
+        <v>20.1275</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6627</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>16.5675</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3267</v>
+        <v>0.4014</v>
       </c>
       <c r="J10" t="n">
-        <v>8.1675</v>
+        <v>10.035</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7165</v>
+        <v>-0.6594</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.9125</v>
+        <v>-16.485</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.03</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1347</v>
+        <v>0.1158</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3675</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1347</v>
+        <v>0.1158</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3675</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1355</v>
+        <v>-0.1028</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.3875</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2764</v>
+        <v>-0.1765</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.91</v>
+        <v>-4.4125</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.68</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5266</v>
+        <v>-0.3434</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.165</v>
+        <v>-8.585000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2406</v>
+        <v>1.1564</v>
       </c>
       <c r="J17" t="n">
-        <v>31.015</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0985</v>
+        <v>1.0675</v>
       </c>
       <c r="J18" t="n">
-        <v>27.4625</v>
+        <v>26.6875</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5132</v>
+        <v>0.5772</v>
       </c>
       <c r="J19" t="n">
-        <v>12.83</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3267</v>
+        <v>0.4014</v>
       </c>
       <c r="J20" t="n">
-        <v>8.1675</v>
+        <v>10.035</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4886</v>
+        <v>-0.4142</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.215</v>
+        <v>-10.355</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.63</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3634</v>
+        <v>0.979</v>
       </c>
       <c r="J22" t="n">
-        <v>27.268</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3249</v>
+        <v>0.9555</v>
       </c>
       <c r="J23" t="n">
-        <v>26.498</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0575</v>
+        <v>0.8015</v>
       </c>
       <c r="J24" t="n">
-        <v>21.15</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7891</v>
+        <v>0.6687</v>
       </c>
       <c r="J25" t="n">
-        <v>15.782</v>
+        <v>13.374</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2052</v>
+        <v>0.3034</v>
       </c>
       <c r="J26" t="n">
-        <v>4.104</v>
+        <v>6.068</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1171</v>
+        <v>0.0859</v>
       </c>
       <c r="J27" t="n">
-        <v>2.342</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.75</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3064</v>
+        <v>-0.2462</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.128</v>
+        <v>-4.924</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.488</v>
+        <v>-0.3392</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.76</v>
+        <v>-6.784</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5513</v>
+        <v>-0.376</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.026</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.5914</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.148</v>
+        <v>-11.828</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4919</v>
+        <v>0.3987</v>
       </c>
       <c r="J32" t="n">
-        <v>14.757</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2912</v>
+        <v>0.248</v>
       </c>
       <c r="J33" t="n">
-        <v>8.736000000000001</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0712</v>
+        <v>-0.0365</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.136</v>
+        <v>-1.095</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3259</v>
+        <v>-0.199</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.776999999999999</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3993</v>
+        <v>-0.2497</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.979</v>
+        <v>-7.491</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.4387</v>
       </c>
       <c r="J37" t="n">
-        <v>17.736</v>
+        <v>13.161</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4359</v>
+        <v>0.3545</v>
       </c>
       <c r="J38" t="n">
-        <v>13.077</v>
+        <v>10.635</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0156</v>
+        <v>0.0373</v>
       </c>
       <c r="J39" t="n">
-        <v>0.468</v>
+        <v>1.119</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.202</v>
+        <v>-0.1101</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.06</v>
+        <v>-3.303</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2849</v>
+        <v>-0.1665</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.547000000000001</v>
+        <v>-4.995</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>1.212</v>
+        <v>0.8542</v>
       </c>
       <c r="J42" t="n">
-        <v>35.148</v>
+        <v>24.7718</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7992</v>
+        <v>0.5905</v>
       </c>
       <c r="J43" t="n">
-        <v>23.1768</v>
+        <v>17.1245</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.524</v>
+        <v>0.4271</v>
       </c>
       <c r="J44" t="n">
-        <v>15.196</v>
+        <v>12.3859</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8334</v>
+        <v>-0.7927</v>
       </c>
       <c r="J45" t="n">
-        <v>-24.1686</v>
+        <v>-22.9883</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.946</v>
+        <v>-0.9161</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.434</v>
+        <v>-26.5669</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.59</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8383</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>24.3107</v>
+        <v>22.0574</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3099</v>
+        <v>0.3502</v>
       </c>
       <c r="J48" t="n">
-        <v>8.9871</v>
+        <v>10.1558</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0997</v>
+        <v>-0.0439</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.8913</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2502</v>
+        <v>-0.1432</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.2558</v>
+        <v>-4.1528</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4419</v>
+        <v>-0.2778</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.8151</v>
+        <v>-8.0562</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.63</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4316</v>
+        <v>1.0085</v>
       </c>
       <c r="J52" t="n">
-        <v>35.79</v>
+        <v>25.2125</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0118</v>
+        <v>0.7474</v>
       </c>
       <c r="J53" t="n">
-        <v>25.295</v>
+        <v>18.685</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6395</v>
+        <v>0.5546</v>
       </c>
       <c r="J54" t="n">
-        <v>15.9875</v>
+        <v>13.865</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1701</v>
+        <v>0.2527</v>
       </c>
       <c r="J55" t="n">
-        <v>4.2525</v>
+        <v>6.3175</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0176</v>
+        <v>0.0974</v>
       </c>
       <c r="J56" t="n">
-        <v>0.44</v>
+        <v>2.435</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2949</v>
+        <v>0.3072</v>
       </c>
       <c r="J57" t="n">
-        <v>7.3725</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0789</v>
+        <v>-0.0849</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.9725</v>
+        <v>-2.1225</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4495</v>
+        <v>-0.2991</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.2375</v>
+        <v>-7.4775</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.64</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.3652</v>
       </c>
       <c r="J60" t="n">
-        <v>-13.7475</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6433</v>
+        <v>-0.4307</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.0825</v>
+        <v>-10.7675</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4924</v>
+        <v>0.3969</v>
       </c>
       <c r="J62" t="n">
-        <v>12.8024</v>
+        <v>10.3194</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0882</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.2932</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.88</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2359</v>
+        <v>-0.1481</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.1334</v>
+        <v>-3.8506</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3496</v>
+        <v>-0.2203</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.089600000000001</v>
+        <v>-5.7278</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4512</v>
+        <v>-0.2893</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.7312</v>
+        <v>-7.5218</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8036</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>20.8936</v>
+        <v>14.612</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.45</v>
       </c>
       <c r="I68" t="n">
-        <v>0.644</v>
+        <v>0.4722</v>
       </c>
       <c r="J68" t="n">
-        <v>16.744</v>
+        <v>12.2772</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2495</v>
+        <v>0.2453</v>
       </c>
       <c r="J69" t="n">
-        <v>6.487</v>
+        <v>6.3778</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2069</v>
+        <v>-0.1088</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.3794</v>
+        <v>-2.8288</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3493</v>
+        <v>-0.209</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.081799999999999</v>
+        <v>-5.434</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6324</v>
+        <v>1.1445</v>
       </c>
       <c r="J72" t="n">
-        <v>42.4424</v>
+        <v>29.757</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9417</v>
+        <v>0.7236</v>
       </c>
       <c r="J73" t="n">
-        <v>24.4842</v>
+        <v>18.8136</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.39</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8934</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>23.2284</v>
+        <v>18.1766</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3272</v>
+        <v>0.3874</v>
       </c>
       <c r="J75" t="n">
-        <v>8.507199999999999</v>
+        <v>10.0724</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.302</v>
+        <v>0.372</v>
       </c>
       <c r="J76" t="n">
-        <v>7.852</v>
+        <v>9.672000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1419</v>
+        <v>-0.1282</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.6894</v>
+        <v>-3.3332</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3367</v>
+        <v>-0.2409</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.754200000000001</v>
+        <v>-6.2634</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.75</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3774</v>
+        <v>-0.2592</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.8124</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.411</v>
+        <v>-0.278</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.686</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.427</v>
+        <v>-0.2874</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.102</v>
+        <v>-7.4724</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0476</v>
+        <v>-0.0683</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.0948</v>
+        <v>-1.5709</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.77</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2978</v>
+        <v>-0.2342</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.8494</v>
+        <v>-5.3866</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.65</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5105</v>
+        <v>-0.3454</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.7415</v>
+        <v>-7.9442</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5105</v>
+        <v>-0.3454</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.7415</v>
+        <v>-7.9442</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5829</v>
+        <v>-0.3922</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.4067</v>
+        <v>-9.0206</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2176</v>
+        <v>1.1509</v>
       </c>
       <c r="J87" t="n">
-        <v>28.0048</v>
+        <v>26.4707</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1571</v>
+        <v>1.114</v>
       </c>
       <c r="J88" t="n">
-        <v>26.6133</v>
+        <v>25.622</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.35</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8247</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>18.9681</v>
+        <v>20.1365</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3916</v>
+        <v>0.4844</v>
       </c>
       <c r="J90" t="n">
-        <v>9.0068</v>
+        <v>11.1412</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2105</v>
+        <v>0.2994</v>
       </c>
       <c r="J91" t="n">
-        <v>4.8415</v>
+        <v>6.8862</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3796</v>
+        <v>0.4233</v>
       </c>
       <c r="J92" t="n">
-        <v>8.3512</v>
+        <v>9.3126</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2529</v>
+        <v>0.2596</v>
       </c>
       <c r="J93" t="n">
-        <v>5.5638</v>
+        <v>5.7112</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.06</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1995</v>
+        <v>0.1928</v>
       </c>
       <c r="J94" t="n">
-        <v>4.389</v>
+        <v>4.2416</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.63</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5894</v>
+        <v>-0.3889</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.9668</v>
+        <v>-8.5558</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.5</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7496</v>
+        <v>-0.5083</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.4912</v>
+        <v>-11.1826</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8169</v>
+        <v>0.8426</v>
       </c>
       <c r="J97" t="n">
-        <v>17.9718</v>
+        <v>18.5372</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.8205</v>
       </c>
       <c r="J98" t="n">
-        <v>17.4416</v>
+        <v>18.051</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.3</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7427</v>
+        <v>0.7762</v>
       </c>
       <c r="J99" t="n">
-        <v>16.3394</v>
+        <v>17.0764</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.25</v>
       </c>
       <c r="I100" t="n">
-        <v>0.597</v>
+        <v>0.6652</v>
       </c>
       <c r="J100" t="n">
-        <v>13.134</v>
+        <v>14.6344</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.18</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4167</v>
+        <v>0.4971</v>
       </c>
       <c r="J101" t="n">
-        <v>9.167400000000001</v>
+        <v>10.9362</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1282</v>
+        <v>0.111</v>
       </c>
       <c r="J102" t="n">
-        <v>3.0768</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.02</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1056</v>
+        <v>0.0843</v>
       </c>
       <c r="J103" t="n">
-        <v>2.5344</v>
+        <v>2.0232</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.194</v>
+        <v>-0.1256</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.656</v>
+        <v>-3.0144</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.9416</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.82</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.9416</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3522</v>
+        <v>1.2244</v>
       </c>
       <c r="J107" t="n">
-        <v>32.4528</v>
+        <v>29.3856</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5541</v>
+        <v>0.5638</v>
       </c>
       <c r="J108" t="n">
-        <v>13.2984</v>
+        <v>13.5312</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.19</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5252</v>
+        <v>0.5397</v>
       </c>
       <c r="J109" t="n">
-        <v>12.6048</v>
+        <v>12.9528</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.094</v>
+        <v>0.1582</v>
       </c>
       <c r="J110" t="n">
-        <v>2.256</v>
+        <v>3.7968</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5232</v>
+        <v>-0.4545</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.5568</v>
+        <v>-10.908</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5109</v>
+        <v>0.4321</v>
       </c>
       <c r="J112" t="n">
-        <v>14.8161</v>
+        <v>12.5309</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.11</v>
       </c>
       <c r="I113" t="n">
-        <v>0.234</v>
+        <v>0.185</v>
       </c>
       <c r="J113" t="n">
-        <v>6.786</v>
+        <v>5.365</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1621</v>
+        <v>0.1267</v>
       </c>
       <c r="J114" t="n">
-        <v>4.7009</v>
+        <v>3.6743</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3162</v>
+        <v>-0.1912</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.1698</v>
+        <v>-5.5448</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3755</v>
+        <v>-0.2322</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.8895</v>
+        <v>-6.7338</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.6969</v>
       </c>
       <c r="J117" t="n">
-        <v>21.1497</v>
+        <v>20.2101</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4046</v>
+        <v>0.3806</v>
       </c>
       <c r="J118" t="n">
-        <v>11.7334</v>
+        <v>11.0374</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.23</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3608</v>
+        <v>0.3423</v>
       </c>
       <c r="J119" t="n">
-        <v>10.4632</v>
+        <v>9.9267</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1472</v>
+        <v>-0.0687</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.2688</v>
+        <v>-1.9923</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1861</v>
+        <v>-0.095</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.3969</v>
+        <v>-2.755</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1938</v>
+        <v>0.1756</v>
       </c>
       <c r="J122" t="n">
-        <v>4.845</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.76</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3478</v>
+        <v>-0.2491</v>
       </c>
       <c r="J123" t="n">
-        <v>-8.695</v>
+        <v>-6.2275</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.73</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4055</v>
+        <v>-0.2767</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.1375</v>
+        <v>-6.9175</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4837</v>
+        <v>-0.3237</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.0925</v>
+        <v>-8.092499999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5966</v>
+        <v>-0.3988</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.915</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.48</v>
       </c>
       <c r="I127" t="n">
-        <v>1.115</v>
+        <v>1.089</v>
       </c>
       <c r="J127" t="n">
-        <v>27.875</v>
+        <v>27.225</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.47</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0941</v>
+        <v>1.0766</v>
       </c>
       <c r="J128" t="n">
-        <v>27.3525</v>
+        <v>26.915</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.43</v>
       </c>
       <c r="I129" t="n">
-        <v>1.009</v>
+        <v>1.0236</v>
       </c>
       <c r="J129" t="n">
-        <v>25.225</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I130" t="n">
-        <v>0.7345</v>
+        <v>0.8118</v>
       </c>
       <c r="J130" t="n">
-        <v>18.3625</v>
+        <v>20.295</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2644</v>
+        <v>-0.177</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.61</v>
+        <v>-4.425</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3109</v>
+        <v>0.3287</v>
       </c>
       <c r="J132" t="n">
-        <v>7.1507</v>
+        <v>7.5601</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1849</v>
+        <v>-0.1535</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.2527</v>
+        <v>-3.5305</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2716</v>
+        <v>-0.2049</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.2468</v>
+        <v>-4.7127</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.404</v>
+        <v>-0.2709</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.292</v>
+        <v>-6.2307</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.5601</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.791</v>
+        <v>-12.8823</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5089</v>
+        <v>1.3323</v>
       </c>
       <c r="J137" t="n">
-        <v>34.7047</v>
+        <v>30.6429</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.42</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0149</v>
+        <v>1.018</v>
       </c>
       <c r="J138" t="n">
-        <v>23.3427</v>
+        <v>23.414</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9274</v>
+        <v>0.9477</v>
       </c>
       <c r="J139" t="n">
-        <v>21.3302</v>
+        <v>21.7971</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0149</v>
+        <v>0.0641</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.3427</v>
+        <v>1.4743</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4433</v>
+        <v>-0.3646</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.1959</v>
+        <v>-8.3858</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8216</v>
+        <v>0.7392</v>
       </c>
       <c r="J142" t="n">
-        <v>20.54</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3312</v>
+        <v>0.3042</v>
       </c>
       <c r="J143" t="n">
-        <v>8.279999999999999</v>
+        <v>7.605</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.31</v>
+        <v>0.2927</v>
       </c>
       <c r="J144" t="n">
-        <v>7.75</v>
+        <v>7.3175</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0809</v>
+        <v>0.1064</v>
       </c>
       <c r="J145" t="n">
-        <v>2.0225</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1726</v>
+        <v>-0.0849</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.315</v>
+        <v>-2.1225</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6153</v>
+        <v>0.5699</v>
       </c>
       <c r="J147" t="n">
-        <v>15.3825</v>
+        <v>14.2475</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1774</v>
+        <v>0.1339</v>
       </c>
       <c r="J148" t="n">
-        <v>4.435</v>
+        <v>3.3475</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.208</v>
+        <v>-0.1284</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.2</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3846</v>
+        <v>-0.2425</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.615</v>
+        <v>-6.0625</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6127</v>
+        <v>-0.4049</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.3175</v>
+        <v>-10.1225</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.07</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2941</v>
+        <v>0.3085</v>
       </c>
       <c r="J152" t="n">
-        <v>6.4702</v>
+        <v>6.787</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.007</v>
+        <v>-0.0402</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.154</v>
+        <v>-0.8844</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.7</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4241</v>
+        <v>-0.2983</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.3302</v>
+        <v>-6.5626</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6622</v>
+        <v>-0.447</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.5684</v>
+        <v>-9.834</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9579</v>
+        <v>-0.6704</v>
       </c>
       <c r="J156" t="n">
-        <v>-21.0738</v>
+        <v>-14.7488</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.92</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8804</v>
+        <v>1.5881</v>
       </c>
       <c r="J157" t="n">
-        <v>41.3688</v>
+        <v>34.9382</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.59</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2886</v>
+        <v>1.2066</v>
       </c>
       <c r="J158" t="n">
-        <v>28.3492</v>
+        <v>26.5452</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0389</v>
+        <v>1.0638</v>
       </c>
       <c r="J159" t="n">
-        <v>22.8558</v>
+        <v>23.4036</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7471</v>
+        <v>0.86</v>
       </c>
       <c r="J160" t="n">
-        <v>16.4362</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.85</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6582</v>
+        <v>-0.5935</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.4804</v>
+        <v>-13.057</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4985</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>14.955</v>
+        <v>17.829</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4176</v>
+        <v>0.4907</v>
       </c>
       <c r="J163" t="n">
-        <v>12.528</v>
+        <v>14.721</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1623</v>
+        <v>0.1926</v>
       </c>
       <c r="J164" t="n">
-        <v>4.869</v>
+        <v>5.778</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2786</v>
+        <v>-0.1635</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.358000000000001</v>
+        <v>-4.905</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3546</v>
+        <v>-0.2161</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.638</v>
+        <v>-6.483</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.39</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0435</v>
+        <v>1.0163</v>
       </c>
       <c r="J167" t="n">
-        <v>31.305</v>
+        <v>30.489</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4383</v>
+        <v>0.428</v>
       </c>
       <c r="J168" t="n">
-        <v>13.149</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.01</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0231</v>
+        <v>0.0303</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0828</v>
+        <v>-0.0245</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.484</v>
+        <v>-0.735</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.272</v>
+        <v>-2.379</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4282</v>
+        <v>0.4869</v>
       </c>
       <c r="J172" t="n">
-        <v>9.848599999999999</v>
+        <v>11.1987</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1375</v>
+        <v>0.1105</v>
       </c>
       <c r="J173" t="n">
-        <v>3.1625</v>
+        <v>2.5415</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.483</v>
+        <v>-0.3161</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.109</v>
+        <v>-7.2703</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.497</v>
+        <v>-0.3257</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.431</v>
+        <v>-7.4911</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6172</v>
+        <v>-0.4103</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.1956</v>
+        <v>-9.4369</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4981</v>
+        <v>1.3265</v>
       </c>
       <c r="J177" t="n">
-        <v>34.4563</v>
+        <v>30.5095</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0239</v>
+        <v>1.0284</v>
       </c>
       <c r="J178" t="n">
-        <v>23.5497</v>
+        <v>23.6532</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8438</v>
+        <v>0.8799</v>
       </c>
       <c r="J179" t="n">
-        <v>19.4074</v>
+        <v>20.2377</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2995</v>
+        <v>0.3868</v>
       </c>
       <c r="J180" t="n">
-        <v>6.8885</v>
+        <v>8.8964</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3599</v>
+        <v>-0.2763</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.277699999999999</v>
+        <v>-6.3549</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.68</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5094</v>
+        <v>1.3348</v>
       </c>
       <c r="J182" t="n">
-        <v>36.2256</v>
+        <v>32.0352</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.5</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1619</v>
+        <v>1.1157</v>
       </c>
       <c r="J183" t="n">
-        <v>27.8856</v>
+        <v>26.7768</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8072</v>
+        <v>0.8556</v>
       </c>
       <c r="J184" t="n">
-        <v>19.3728</v>
+        <v>20.5344</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.32</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7462</v>
+        <v>0.8133</v>
       </c>
       <c r="J185" t="n">
-        <v>17.9088</v>
+        <v>19.5192</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8024</v>
+        <v>-0.7532</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.2576</v>
+        <v>-18.0768</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.1792</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.1792</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1108</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.6592</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3062</v>
+        <v>-0.196</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.3488</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3062</v>
+        <v>-0.196</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.3488</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4747</v>
+        <v>1.3222</v>
       </c>
       <c r="J192" t="n">
-        <v>32.4434</v>
+        <v>29.0884</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.3808</v>
+        <v>1.2639</v>
       </c>
       <c r="J193" t="n">
-        <v>30.3776</v>
+        <v>27.8058</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.43</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9251</v>
+        <v>1.0105</v>
       </c>
       <c r="J194" t="n">
-        <v>20.3522</v>
+        <v>22.231</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8095</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>17.809</v>
+        <v>20.2818</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1239</v>
+        <v>0.2182</v>
       </c>
       <c r="J196" t="n">
-        <v>2.7258</v>
+        <v>4.8004</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.84</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1627</v>
+        <v>-0.1507</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.5794</v>
+        <v>-3.3154</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.79</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2428</v>
+        <v>-0.2051</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.3416</v>
+        <v>-4.5122</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.64</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3483</v>
       </c>
       <c r="J199" t="n">
-        <v>-11.099</v>
+        <v>-7.6626</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.61</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5513</v>
+        <v>-0.376</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.1286</v>
+        <v>-8.272</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.5</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7052</v>
+        <v>-0.4788</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.5144</v>
+        <v>-10.5336</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.22</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4346</v>
+        <v>0.499</v>
       </c>
       <c r="J202" t="n">
-        <v>11.7342</v>
+        <v>13.473</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3012</v>
+        <v>0.326</v>
       </c>
       <c r="J203" t="n">
-        <v>8.132400000000001</v>
+        <v>8.802</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3368</v>
+        <v>-0.2112</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.0936</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4251</v>
+        <v>-0.2709</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.4777</v>
+        <v>-7.3143</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.75</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4392</v>
+        <v>-0.2806</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.8584</v>
+        <v>-7.5762</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8807</v>
+        <v>1.5884</v>
       </c>
       <c r="J207" t="n">
-        <v>50.7789</v>
+        <v>42.8868</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.31</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8511</v>
+        <v>0.8371</v>
       </c>
       <c r="J208" t="n">
-        <v>22.9797</v>
+        <v>22.6017</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.14</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4095</v>
+        <v>0.4224</v>
       </c>
       <c r="J209" t="n">
-        <v>11.0565</v>
+        <v>11.4048</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.92</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3982</v>
+        <v>-0.3279</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.7514</v>
+        <v>-8.853300000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.4098</v>
+        <v>-1.4462</v>
       </c>
       <c r="J211" t="n">
-        <v>-38.0646</v>
+        <v>-39.0474</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5003</v>
+        <v>0.455</v>
       </c>
       <c r="J212" t="n">
-        <v>32.5195</v>
+        <v>29.575</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.06</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2578</v>
+        <v>0.2245</v>
       </c>
       <c r="J213" t="n">
-        <v>16.757</v>
+        <v>14.5925</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0429</v>
+        <v>0.0511</v>
       </c>
       <c r="J214" t="n">
-        <v>2.7885</v>
+        <v>3.3215</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.01</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0429</v>
+        <v>0.0511</v>
       </c>
       <c r="J215" t="n">
-        <v>2.7885</v>
+        <v>3.3215</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.518</v>
+        <v>-0.4659</v>
       </c>
       <c r="J216" t="n">
-        <v>-33.67</v>
+        <v>-30.2835</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4143</v>
+        <v>0.488</v>
       </c>
       <c r="J217" t="n">
-        <v>26.9295</v>
+        <v>31.72</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1764</v>
+        <v>0.2113</v>
       </c>
       <c r="J218" t="n">
-        <v>11.466</v>
+        <v>13.7345</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1088</v>
+        <v>0.1504</v>
       </c>
       <c r="J219" t="n">
-        <v>7.072</v>
+        <v>9.776</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0219</v>
+        <v>0.0555</v>
       </c>
       <c r="J220" t="n">
-        <v>1.4235</v>
+        <v>3.6075</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1202</v>
+        <v>-0.0575</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.813</v>
+        <v>-3.7375</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.77</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6471</v>
+        <v>1.4281</v>
       </c>
       <c r="J222" t="n">
-        <v>32.942</v>
+        <v>28.562</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.68</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4838</v>
+        <v>1.3224</v>
       </c>
       <c r="J223" t="n">
-        <v>29.676</v>
+        <v>26.448</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8008</v>
+        <v>0.8907</v>
       </c>
       <c r="J224" t="n">
-        <v>16.016</v>
+        <v>17.814</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4228</v>
+        <v>0.5239</v>
       </c>
       <c r="J225" t="n">
-        <v>8.456</v>
+        <v>10.478</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5209</v>
+        <v>-0.4446</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.418</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.48</v>
+        <v>0.5625</v>
       </c>
       <c r="J227" t="n">
-        <v>9.6</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2006</v>
+        <v>-0.1685</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.012</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.62</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.5667</v>
+        <v>-0.3788</v>
       </c>
       <c r="J229" t="n">
-        <v>-11.334</v>
+        <v>-7.576</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5805</v>
+        <v>-0.3882</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.61</v>
+        <v>-7.764</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.49</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7372</v>
+        <v>-0.5</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.744</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4561</v>
+        <v>1.2938</v>
       </c>
       <c r="J232" t="n">
-        <v>40.7708</v>
+        <v>36.2264</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6189</v>
+        <v>0.6309</v>
       </c>
       <c r="J233" t="n">
-        <v>17.3292</v>
+        <v>17.6652</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2372</v>
+        <v>0.303</v>
       </c>
       <c r="J234" t="n">
-        <v>6.6416</v>
+        <v>8.484</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0843</v>
+        <v>0.1528</v>
       </c>
       <c r="J235" t="n">
-        <v>2.3604</v>
+        <v>4.2784</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1811</v>
+        <v>-0.1031</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.0708</v>
+        <v>-2.8868</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.3</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5446</v>
+        <v>0.647</v>
       </c>
       <c r="J237" t="n">
-        <v>15.2488</v>
+        <v>18.116</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2201</v>
+        <v>0.2241</v>
       </c>
       <c r="J238" t="n">
-        <v>6.1628</v>
+        <v>6.2748</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3349</v>
+        <v>-0.2105</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.3772</v>
+        <v>-5.894</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3502</v>
+        <v>-0.2206</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.8056</v>
+        <v>-6.1768</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5846</v>
+        <v>-0.3845</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.3688</v>
+        <v>-10.766</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2112/event_2112_evp_summary.xlsx
+++ b/database/event/2112/event_2112_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2919</v>
+        <v>6.4722</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7072</v>
+        <v>1.7562</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2025</v>
+        <v>2.3221</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2919</v>
+        <v>6.4722</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4124</v>
+        <v>2.3564</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8795</v>
+        <v>4.1158</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0135</v>
+        <v>2.8804</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5669</v>
+        <v>1.5554</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8795</v>
+        <v>4.1158</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>129</v>
       </c>
       <c r="M2" t="n">
-        <v>5.446400000000001</v>
+        <v>5.6712</v>
       </c>
       <c r="N2" t="n">
         <v>179</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8752</v>
+        <v>5.9736</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5942</v>
+        <v>1.6209</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0143</v>
+        <v>2.0951</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8752</v>
+        <v>5.9736</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9851</v>
+        <v>2.9279</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8901</v>
+        <v>3.0456</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0312</v>
+        <v>4.7662</v>
       </c>
       <c r="I3" t="n">
-        <v>2.616</v>
+        <v>2.5737</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8901</v>
+        <v>3.0456</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -575,7 +575,7 @@
         <v>129</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5061</v>
+        <v>5.6193</v>
       </c>
       <c r="N3" t="n">
         <v>179</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9829</v>
+        <v>4.9893</v>
       </c>
       <c r="C4" t="n">
-        <v>1.352</v>
+        <v>1.3538</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6115</v>
+        <v>1.647</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9829</v>
+        <v>4.9893</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6977</v>
+        <v>3.5947</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2852</v>
+        <v>1.3946</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5422</v>
+        <v>6.966</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9216</v>
+        <v>3.7616</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2852</v>
+        <v>1.3946</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2068</v>
+        <v>5.1562</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4172</v>
+        <v>4.4569</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1986</v>
+        <v>1.2093</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3561</v>
+        <v>1.4047</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4172</v>
+        <v>4.4569</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8031</v>
+        <v>2.7349</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6141</v>
+        <v>1.722</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3901</v>
+        <v>4.1293</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2826</v>
+        <v>2.2298</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6141</v>
+        <v>1.722</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>127</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8967</v>
+        <v>3.9518</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6952</v>
+        <v>3.5992</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0026</v>
+        <v>0.9766</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0302</v>
+        <v>1.0142</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6952</v>
+        <v>3.5992</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8875</v>
+        <v>2.393</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1923</v>
+        <v>1.2062</v>
       </c>
       <c r="H6" t="n">
-        <v>8.210900000000001</v>
+        <v>3.0013</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2693</v>
+        <v>1.6207</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1923</v>
+        <v>1.2062</v>
       </c>
       <c r="K6" t="n">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>4.077</v>
+        <v>2.8269</v>
       </c>
       <c r="N6" t="n">
-        <v>221</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5567</v>
+        <v>3.5899</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9651</v>
+        <v>0.9741</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9677</v>
+        <v>1.01</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5567</v>
+        <v>3.5899</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8095</v>
+        <v>3.7947</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2528</v>
+        <v>-0.2048</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9359</v>
+        <v>7.626</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1263</v>
+        <v>4.118</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2528</v>
+        <v>-0.2048</v>
       </c>
       <c r="K7" t="n">
         <v>142</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.873499999999999</v>
+        <v>3.9132</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5348</v>
+        <v>3.4709</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9591</v>
+        <v>0.9418</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9578</v>
+        <v>0.9558</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5348</v>
+        <v>3.4709</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4873</v>
+        <v>3.7408</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0475</v>
+        <v>-0.2699</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2772</v>
+        <v>7.4483</v>
       </c>
       <c r="I8" t="n">
-        <v>1.704</v>
+        <v>4.022</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0475</v>
+        <v>-0.2699</v>
       </c>
       <c r="K8" t="n">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="L8" t="n">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7515</v>
+        <v>3.7521</v>
       </c>
       <c r="N8" t="n">
-        <v>171</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3463</v>
+        <v>3.3691</v>
       </c>
       <c r="C9" t="n">
-        <v>0.908</v>
+        <v>0.9142</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8727</v>
+        <v>0.9095</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3463</v>
+        <v>3.3691</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7452</v>
+        <v>1.6134</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6011</v>
+        <v>1.7557</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7452</v>
+        <v>1.6134</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9074</v>
+        <v>0.8712</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6011</v>
+        <v>1.7557</v>
       </c>
       <c r="K9" t="n">
         <v>50</v>
@@ -851,7 +851,7 @@
         <v>129</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5085</v>
+        <v>2.6269</v>
       </c>
       <c r="N9" t="n">
         <v>179</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3258</v>
+        <v>3.3098</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9024</v>
+        <v>0.8981</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8825</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3258</v>
+        <v>3.3098</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9015</v>
+        <v>1.581</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4243</v>
+        <v>1.7288</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7368</v>
+        <v>1.581</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4629</v>
+        <v>0.8537</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4243</v>
+        <v>1.7288</v>
       </c>
       <c r="K10" t="n">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8872</v>
+        <v>2.5825</v>
       </c>
       <c r="N10" t="n">
-        <v>273</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2762</v>
+        <v>3.2863</v>
       </c>
       <c r="C11" t="n">
-        <v>0.889</v>
+        <v>0.8917</v>
       </c>
       <c r="D11" t="n">
-        <v>0.841</v>
+        <v>0.8718</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2762</v>
+        <v>3.2863</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0076</v>
+        <v>2.9544</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2686</v>
+        <v>0.3319</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1105</v>
+        <v>4.8536</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6572</v>
+        <v>2.6209</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2686</v>
+        <v>0.3319</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>127</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9258</v>
+        <v>2.9528</v>
       </c>
       <c r="N11" t="n">
         <v>171</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.269</v>
+        <v>3.265</v>
       </c>
       <c r="C12" t="n">
-        <v>0.887</v>
+        <v>0.8859</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8378</v>
+        <v>0.8621</v>
       </c>
       <c r="E12" t="n">
-        <v>3.269</v>
+        <v>3.265</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4212</v>
+        <v>2.8572</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1522</v>
+        <v>0.4078</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5677</v>
+        <v>4.5328</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4149</v>
+        <v>2.4477</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1522</v>
+        <v>0.4078</v>
       </c>
       <c r="K12" t="n">
         <v>196</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2627</v>
+        <v>2.8555</v>
       </c>
       <c r="N12" t="n">
         <v>273</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2304</v>
+        <v>3.2371</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8783</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8204</v>
+        <v>0.8494</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2304</v>
+        <v>3.2371</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0573</v>
+        <v>3.3574</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8269</v>
+        <v>-0.1203</v>
       </c>
       <c r="H13" t="n">
-        <v>8.808999999999999</v>
+        <v>6.1831</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5803</v>
+        <v>3.3388</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8269</v>
+        <v>-0.1203</v>
       </c>
       <c r="K13" t="n">
         <v>196</v>
@@ -1035,7 +1035,7 @@
         <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7534</v>
+        <v>3.2185</v>
       </c>
       <c r="N13" t="n">
         <v>273</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1731</v>
+        <v>3.0957</v>
       </c>
       <c r="C14" t="n">
-        <v>0.861</v>
+        <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7945</v>
+        <v>0.785</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1731</v>
+        <v>3.0957</v>
       </c>
       <c r="F14" t="n">
-        <v>1.633</v>
+        <v>3.9596</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5401</v>
+        <v>-0.8639</v>
       </c>
       <c r="H14" t="n">
-        <v>1.633</v>
+        <v>8.1701</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8491</v>
+        <v>4.4118</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5401</v>
+        <v>-0.8639</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="L14" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3892</v>
+        <v>3.5479</v>
       </c>
       <c r="N14" t="n">
-        <v>179</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5202</v>
+        <v>2.4438</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6838</v>
+        <v>0.6631</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4997</v>
+        <v>0.4883</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5202</v>
+        <v>2.4438</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9003</v>
+        <v>2.8128</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3801</v>
+        <v>-0.369</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7325</v>
+        <v>4.3864</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4607</v>
+        <v>2.3686</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3801</v>
+        <v>-0.369</v>
       </c>
       <c r="K15" t="n">
         <v>142</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0806</v>
+        <v>1.9996</v>
       </c>
       <c r="N15" t="n">
         <v>221</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2459</v>
+        <v>2.1205</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5754</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3759</v>
+        <v>0.3411</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2459</v>
+        <v>2.1205</v>
       </c>
       <c r="F16" t="n">
-        <v>3.032</v>
+        <v>2.952</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7861</v>
+        <v>-0.8315</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1964</v>
+        <v>4.8454</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7019</v>
+        <v>2.6165</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7861</v>
+        <v>-0.8315</v>
       </c>
       <c r="K16" t="n">
         <v>196</v>
@@ -1173,7 +1173,7 @@
         <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9158</v>
+        <v>1.785</v>
       </c>
       <c r="N16" t="n">
         <v>273</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5954</v>
+        <v>1.5312</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4329</v>
+        <v>0.4155</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0822</v>
+        <v>0.0728</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5954</v>
+        <v>1.5312</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0669</v>
+        <v>1.936</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4715</v>
+        <v>-0.4048</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0669</v>
+        <v>1.936</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0747</v>
+        <v>1.0454</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4715</v>
+        <v>-0.4048</v>
       </c>
       <c r="K17" t="n">
         <v>50</v>
@@ -1219,7 +1219,7 @@
         <v>129</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6032</v>
+        <v>0.6406000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>179</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2971</v>
+        <v>1.4781</v>
       </c>
       <c r="C18" t="n">
-        <v>0.352</v>
+        <v>0.4011</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0524</v>
+        <v>0.0487</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2971</v>
+        <v>1.4781</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2907</v>
+        <v>-0.3139</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0064</v>
+        <v>1.792</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2907</v>
+        <v>-0.3139</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6711</v>
+        <v>-0.1695</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0064</v>
+        <v>1.792</v>
       </c>
       <c r="K18" t="n">
         <v>44</v>
@@ -1265,7 +1265,7 @@
         <v>127</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6775</v>
+        <v>1.6225</v>
       </c>
       <c r="N18" t="n">
         <v>171</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>spaze</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2017</v>
+        <v>1.2678</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3261</v>
+        <v>0.344</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0955</v>
+        <v>-0.0471</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2017</v>
+        <v>1.2678</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2017</v>
+        <v>1.2454</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2017</v>
+        <v>1.2454</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2017</v>
+        <v>0.6725</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="K19" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2017</v>
+        <v>0.6949</v>
       </c>
       <c r="N19" t="n">
-        <v>81</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>spaze</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1942</v>
+        <v>1.1777</v>
       </c>
       <c r="C20" t="n">
-        <v>0.324</v>
+        <v>0.3196</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0989</v>
+        <v>-0.0881</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1942</v>
+        <v>1.1777</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.441</v>
+        <v>1.1777</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.441</v>
+        <v>1.1777</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2293</v>
+        <v>1.1777</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="L20" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4059</v>
+        <v>1.1777</v>
       </c>
       <c r="N20" t="n">
-        <v>171</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="C21" t="n">
-        <v>0.251</v>
+        <v>0.2355</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2203</v>
+        <v>-0.229</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9252</v>
+        <v>0.8681</v>
       </c>
       <c r="N21" t="n">
         <v>81</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2066</v>
+        <v>0.1947</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2943</v>
+        <v>-0.2976</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7614</v>
+        <v>0.7174</v>
       </c>
       <c r="N22" t="n">
         <v>90</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2039</v>
+        <v>0.1946</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2987</v>
+        <v>-0.2978</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7516</v>
+        <v>0.7171</v>
       </c>
       <c r="N23" t="n">
         <v>96</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1864</v>
+        <v>0.1722</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3279</v>
+        <v>-0.3353</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="N24" t="n">
         <v>96</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1808</v>
+        <v>0.1566</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3371</v>
+        <v>-0.3614</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6665</v>
+        <v>0.5773</v>
       </c>
       <c r="N25" t="n">
         <v>96</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508</v>
+        <v>0.1388</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3871</v>
+        <v>-0.3914</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="N26" t="n">
         <v>165</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="C27" t="n">
-        <v>0.115</v>
+        <v>0.0987</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4467</v>
+        <v>-0.4586</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4238</v>
+        <v>0.3637</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0224</v>
+        <v>0.0199</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6008</v>
+        <v>-0.5908</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0825</v>
+        <v>0.0733</v>
       </c>
       <c r="N28" t="n">
         <v>81</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.097</v>
+        <v>-0.1116</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7994</v>
+        <v>-0.8114</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3575</v>
+        <v>-0.4112</v>
       </c>
       <c r="N29" t="n">
         <v>90</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1085</v>
+        <v>-0.1241</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8186</v>
+        <v>-0.8324</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4</v>
+        <v>-0.4573</v>
       </c>
       <c r="N30" t="n">
         <v>165</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5017</v>
+        <v>-0.4889</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1361</v>
+        <v>-0.1327</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8645</v>
+        <v>-0.8468</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5017</v>
+        <v>-0.4889</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5017</v>
+        <v>-0.7691</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.2802</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5017</v>
+        <v>-0.7691</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5017</v>
+        <v>-0.4153</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2802</v>
       </c>
       <c r="K31" t="n">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5017</v>
+        <v>-0.1351</v>
       </c>
       <c r="N31" t="n">
-        <v>165</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1517</v>
+        <v>-0.1462</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8904</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6956</v>
+        <v>-0.5764</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1887</v>
+        <v>-0.1564</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.952</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6956</v>
+        <v>-0.5764</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9318</v>
+        <v>-0.5764</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2362</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9318</v>
+        <v>-0.5764</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4845</v>
+        <v>-0.5764</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2362</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2483</v>
+        <v>-0.5764</v>
       </c>
       <c r="N33" t="n">
-        <v>273</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1959</v>
+        <v>-0.2075</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9639</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7218</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>165</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2041</v>
+        <v>-0.2157</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9776</v>
+        <v>-0.9861</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7523</v>
+        <v>-0.795</v>
       </c>
       <c r="N35" t="n">
         <v>81</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9656</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.251</v>
+        <v>-0.262</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0556</v>
+        <v>-1.0638</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9656</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.1987</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.7669</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.1987</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.1073</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.7669</v>
       </c>
       <c r="K36" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.8742000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>90</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.26</v>
+        <v>-0.2668</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0706</v>
+        <v>-1.0719</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9583</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.995</v>
+        <v>-0.993</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.27</v>
+        <v>-0.2694</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0872</v>
+        <v>-1.0762</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.995</v>
+        <v>-0.993</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2679</v>
+        <v>-0.993</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7271</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2679</v>
+        <v>-0.993</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1393</v>
+        <v>-0.993</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7271</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="L38" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.993</v>
       </c>
       <c r="N38" t="n">
-        <v>221</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3463</v>
+        <v>-0.3507</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2141</v>
+        <v>-1.2126</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2761</v>
+        <v>-1.2925</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.387</v>
+        <v>-0.3853</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2819</v>
+        <v>-1.2706</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4263</v>
+        <v>-1.4199</v>
       </c>
       <c r="N40" t="n">
         <v>90</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6899</v>
+        <v>-0.6592</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7859</v>
+        <v>-1.7302</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5427</v>
+        <v>-2.4295</v>
       </c>
       <c r="N41" t="n">
         <v>96</v>
@@ -2429,10 +2429,10 @@
         <v>1.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4649</v>
+        <v>0.4421</v>
       </c>
       <c r="J2" t="n">
-        <v>11.6225</v>
+        <v>11.0525</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0646</v>
+        <v>-0.081</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.615</v>
+        <v>-2.025</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2543</v>
+        <v>-0.2726</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.3575</v>
+        <v>-6.815</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3872</v>
+        <v>-0.401</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.68</v>
+        <v>-10.025</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.55</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4523</v>
+        <v>-0.4629</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.3075</v>
+        <v>-11.5725</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3793</v>
+        <v>1.4809</v>
       </c>
       <c r="J7" t="n">
-        <v>34.4825</v>
+        <v>37.0225</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8051</v>
+        <v>0.7653</v>
       </c>
       <c r="J8" t="n">
-        <v>20.1275</v>
+        <v>19.1325</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6651</v>
       </c>
       <c r="J9" t="n">
-        <v>17.3</v>
+        <v>16.6275</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4014</v>
+        <v>0.4032</v>
       </c>
       <c r="J10" t="n">
-        <v>10.035</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6594</v>
+        <v>-0.6095</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.485</v>
+        <v>-15.2375</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.03</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1158</v>
+        <v>0.1174</v>
       </c>
       <c r="J12" t="n">
-        <v>2.895</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1158</v>
+        <v>0.1174</v>
       </c>
       <c r="J13" t="n">
-        <v>2.895</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1028</v>
+        <v>-0.1169</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.57</v>
+        <v>-2.9225</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1765</v>
+        <v>-0.1926</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.4125</v>
+        <v>-4.815</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.68</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3434</v>
+        <v>-0.3568</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.585000000000001</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1564</v>
+        <v>1.164</v>
       </c>
       <c r="J17" t="n">
-        <v>28.91</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0675</v>
+        <v>1.0346</v>
       </c>
       <c r="J18" t="n">
-        <v>26.6875</v>
+        <v>25.865</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5772</v>
+        <v>0.5621</v>
       </c>
       <c r="J19" t="n">
-        <v>14.43</v>
+        <v>14.0525</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4014</v>
+        <v>0.4032</v>
       </c>
       <c r="J20" t="n">
-        <v>10.035</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4142</v>
+        <v>-0.3877</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.355</v>
+        <v>-9.692500000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.63</v>
       </c>
       <c r="I22" t="n">
-        <v>0.979</v>
+        <v>1.0855</v>
       </c>
       <c r="J22" t="n">
-        <v>19.58</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9555</v>
+        <v>1.0603</v>
       </c>
       <c r="J23" t="n">
-        <v>19.11</v>
+        <v>21.206</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8015</v>
+        <v>0.8939</v>
       </c>
       <c r="J24" t="n">
-        <v>16.03</v>
+        <v>17.878</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6687</v>
+        <v>0.7482</v>
       </c>
       <c r="J25" t="n">
-        <v>13.374</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3034</v>
+        <v>0.3233</v>
       </c>
       <c r="J26" t="n">
-        <v>6.068</v>
+        <v>6.466</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0859</v>
+        <v>0.0471</v>
       </c>
       <c r="J27" t="n">
-        <v>1.718</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.75</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2462</v>
+        <v>-0.2684</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.924</v>
+        <v>-5.368</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3392</v>
+        <v>-0.3587</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.784</v>
+        <v>-7.174</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.376</v>
+        <v>-0.3939</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.52</v>
+        <v>-7.878</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5914</v>
+        <v>-0.5956</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.828</v>
+        <v>-11.912</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3987</v>
+        <v>0.4385</v>
       </c>
       <c r="J32" t="n">
-        <v>11.961</v>
+        <v>13.155</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.248</v>
+        <v>0.256</v>
       </c>
       <c r="J33" t="n">
-        <v>7.44</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0365</v>
+        <v>-0.0431</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.095</v>
+        <v>-1.293</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.199</v>
+        <v>-0.2124</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.97</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2497</v>
+        <v>-0.2628</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.491</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4387</v>
+        <v>0.4961</v>
       </c>
       <c r="J37" t="n">
-        <v>13.161</v>
+        <v>14.883</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3545</v>
+        <v>0.3805</v>
       </c>
       <c r="J38" t="n">
-        <v>10.635</v>
+        <v>11.415</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0373</v>
+        <v>0.0473</v>
       </c>
       <c r="J39" t="n">
-        <v>1.119</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1101</v>
+        <v>-0.1193</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.303</v>
+        <v>-3.579</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1665</v>
+        <v>-0.1774</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.995</v>
+        <v>-5.322</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8542</v>
+        <v>0.9351</v>
       </c>
       <c r="J42" t="n">
-        <v>24.7718</v>
+        <v>27.1179</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5905</v>
+        <v>0.6491</v>
       </c>
       <c r="J43" t="n">
-        <v>17.1245</v>
+        <v>18.8239</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4271</v>
+        <v>0.4667</v>
       </c>
       <c r="J44" t="n">
-        <v>12.3859</v>
+        <v>13.5343</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7927</v>
+        <v>-0.7353</v>
       </c>
       <c r="J45" t="n">
-        <v>-22.9883</v>
+        <v>-21.3237</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9161</v>
+        <v>-0.8429</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.5669</v>
+        <v>-24.4441</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.59</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.8514</v>
       </c>
       <c r="J47" t="n">
-        <v>22.0574</v>
+        <v>24.6906</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3502</v>
+        <v>0.3665</v>
       </c>
       <c r="J48" t="n">
-        <v>10.1558</v>
+        <v>10.6285</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0439</v>
+        <v>-0.0488</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.2731</v>
+        <v>-1.4152</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1432</v>
+        <v>-0.1539</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.1528</v>
+        <v>-4.4631</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2778</v>
+        <v>-0.2889</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.0562</v>
+        <v>-8.3781</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.63</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0085</v>
+        <v>1.1114</v>
       </c>
       <c r="J52" t="n">
-        <v>25.2125</v>
+        <v>27.785</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7474</v>
+        <v>0.8306</v>
       </c>
       <c r="J53" t="n">
-        <v>18.685</v>
+        <v>20.765</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5546</v>
+        <v>0.6179</v>
       </c>
       <c r="J54" t="n">
-        <v>13.865</v>
+        <v>15.4475</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2527</v>
+        <v>0.269</v>
       </c>
       <c r="J55" t="n">
-        <v>6.3175</v>
+        <v>6.725</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0974</v>
+        <v>0.1226</v>
       </c>
       <c r="J56" t="n">
-        <v>2.435</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3072</v>
+        <v>0.2926</v>
       </c>
       <c r="J57" t="n">
-        <v>7.68</v>
+        <v>7.315</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0849</v>
+        <v>-0.103</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.1225</v>
+        <v>-2.575</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2991</v>
+        <v>-0.3168</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.4775</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.64</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3652</v>
+        <v>-0.3805</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.512499999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4307</v>
+        <v>-0.4429</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.7675</v>
+        <v>-11.0725</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3969</v>
+        <v>0.4322</v>
       </c>
       <c r="J62" t="n">
-        <v>10.3194</v>
+        <v>11.2372</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.82</v>
+        <v>-2.1216</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.88</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1481</v>
+        <v>-0.1631</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.8506</v>
+        <v>-4.2406</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2203</v>
+        <v>-0.2357</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.7278</v>
+        <v>-6.1282</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2893</v>
+        <v>-0.3036</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.5218</v>
+        <v>-7.8936</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6434</v>
       </c>
       <c r="J67" t="n">
-        <v>14.612</v>
+        <v>16.7284</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.45</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4722</v>
+        <v>0.5385</v>
       </c>
       <c r="J68" t="n">
-        <v>12.2772</v>
+        <v>14.001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2453</v>
+        <v>0.2631</v>
       </c>
       <c r="J69" t="n">
-        <v>6.3778</v>
+        <v>6.8406</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1088</v>
+        <v>-0.1151</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.8288</v>
+        <v>-2.9926</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.209</v>
+        <v>-0.218</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.434</v>
+        <v>-5.668</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1445</v>
+        <v>1.259</v>
       </c>
       <c r="J72" t="n">
-        <v>29.757</v>
+        <v>32.734</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7236</v>
+        <v>0.8073</v>
       </c>
       <c r="J73" t="n">
-        <v>18.8136</v>
+        <v>20.9898</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.39</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7803</v>
       </c>
       <c r="J74" t="n">
-        <v>18.1766</v>
+        <v>20.2878</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3874</v>
+        <v>0.4286</v>
       </c>
       <c r="J75" t="n">
-        <v>10.0724</v>
+        <v>11.1436</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.372</v>
+        <v>0.4065</v>
       </c>
       <c r="J76" t="n">
-        <v>9.672000000000001</v>
+        <v>10.569</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1282</v>
+        <v>-0.1479</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.3332</v>
+        <v>-3.8454</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2409</v>
+        <v>-0.2602</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.2634</v>
+        <v>-6.7652</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.75</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2592</v>
+        <v>-0.2783</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.7392</v>
+        <v>-7.2358</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.278</v>
+        <v>-0.2967</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.228</v>
+        <v>-7.7142</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2874</v>
+        <v>-0.3059</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.4724</v>
+        <v>-7.9534</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0683</v>
+        <v>-0.0901</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.5709</v>
+        <v>-2.0723</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.77</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2342</v>
+        <v>-0.2551</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.3866</v>
+        <v>-5.8673</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.65</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3454</v>
+        <v>-0.3635</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.9442</v>
+        <v>-8.3605</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3454</v>
+        <v>-0.3635</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.9442</v>
+        <v>-8.3605</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3922</v>
+        <v>-0.4081</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.0206</v>
+        <v>-9.3863</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1509</v>
+        <v>1.1199</v>
       </c>
       <c r="J87" t="n">
-        <v>26.4707</v>
+        <v>25.7577</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.114</v>
+        <v>1.0801</v>
       </c>
       <c r="J88" t="n">
-        <v>25.622</v>
+        <v>24.8423</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.35</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8306</v>
       </c>
       <c r="J89" t="n">
-        <v>20.1365</v>
+        <v>19.1038</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4844</v>
+        <v>0.4827</v>
       </c>
       <c r="J90" t="n">
-        <v>11.1412</v>
+        <v>11.1021</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2994</v>
+        <v>0.3144</v>
       </c>
       <c r="J91" t="n">
-        <v>6.8862</v>
+        <v>7.2312</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4233</v>
+        <v>0.4114</v>
       </c>
       <c r="J92" t="n">
-        <v>9.3126</v>
+        <v>9.050800000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2596</v>
+        <v>0.2573</v>
       </c>
       <c r="J93" t="n">
-        <v>5.7112</v>
+        <v>5.6606</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.06</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1928</v>
+        <v>0.1927</v>
       </c>
       <c r="J94" t="n">
-        <v>4.2416</v>
+        <v>4.2394</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.63</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3889</v>
+        <v>-0.4007</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.5558</v>
+        <v>-8.8154</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.5</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5083</v>
+        <v>-0.5142</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.1826</v>
+        <v>-11.3124</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8426</v>
+        <v>0.7996</v>
       </c>
       <c r="J97" t="n">
-        <v>18.5372</v>
+        <v>17.5912</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8205</v>
+        <v>0.7802</v>
       </c>
       <c r="J98" t="n">
-        <v>18.051</v>
+        <v>17.1644</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.3</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7762</v>
+        <v>0.7411</v>
       </c>
       <c r="J99" t="n">
-        <v>17.0764</v>
+        <v>16.3042</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.25</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6652</v>
+        <v>0.6421</v>
       </c>
       <c r="J100" t="n">
-        <v>14.6344</v>
+        <v>14.1262</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.18</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4971</v>
+        <v>0.4915</v>
       </c>
       <c r="J101" t="n">
-        <v>10.9362</v>
+        <v>10.813</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.111</v>
+        <v>0.1139</v>
       </c>
       <c r="J102" t="n">
-        <v>2.664</v>
+        <v>2.7336</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.02</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0843</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>2.0232</v>
+        <v>2.076</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1256</v>
+        <v>-0.1403</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.0144</v>
+        <v>-3.3672</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.016</v>
+        <v>-5.3928</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.82</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.016</v>
+        <v>-5.3928</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2244</v>
+        <v>1.1917</v>
       </c>
       <c r="J107" t="n">
-        <v>29.3856</v>
+        <v>28.6008</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5638</v>
+        <v>0.5476</v>
       </c>
       <c r="J108" t="n">
-        <v>13.5312</v>
+        <v>13.1424</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.19</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5397</v>
+        <v>0.5259</v>
       </c>
       <c r="J109" t="n">
-        <v>12.9528</v>
+        <v>12.6216</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1582</v>
+        <v>0.1736</v>
       </c>
       <c r="J110" t="n">
-        <v>3.7968</v>
+        <v>4.1664</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4545</v>
+        <v>-0.4281</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.908</v>
+        <v>-10.2744</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4321</v>
+        <v>0.4383</v>
       </c>
       <c r="J112" t="n">
-        <v>12.5309</v>
+        <v>12.7107</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.11</v>
       </c>
       <c r="I113" t="n">
-        <v>0.185</v>
+        <v>0.1984</v>
       </c>
       <c r="J113" t="n">
-        <v>5.365</v>
+        <v>5.7536</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1267</v>
+        <v>0.1393</v>
       </c>
       <c r="J114" t="n">
-        <v>3.6743</v>
+        <v>4.0397</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1912</v>
+        <v>-0.204</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.5448</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2322</v>
+        <v>-0.245</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.7338</v>
+        <v>-7.105</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6969</v>
+        <v>0.6829</v>
       </c>
       <c r="J117" t="n">
-        <v>20.2101</v>
+        <v>19.8041</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3806</v>
+        <v>0.3895</v>
       </c>
       <c r="J118" t="n">
-        <v>11.0374</v>
+        <v>11.2955</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.23</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3423</v>
+        <v>0.3531</v>
       </c>
       <c r="J119" t="n">
-        <v>9.9267</v>
+        <v>10.2399</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0687</v>
+        <v>-0.0726</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.9923</v>
+        <v>-2.1054</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.095</v>
+        <v>-0.1009</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.755</v>
+        <v>-2.9261</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1756</v>
+        <v>0.1612</v>
       </c>
       <c r="J122" t="n">
-        <v>4.39</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.76</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2491</v>
+        <v>-0.2686</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.2275</v>
+        <v>-6.715</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.73</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2767</v>
+        <v>-0.2958</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.9175</v>
+        <v>-7.395</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3237</v>
+        <v>-0.3413</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.092499999999999</v>
+        <v>-8.532500000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3988</v>
+        <v>-0.4133</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.3325</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.48</v>
       </c>
       <c r="I127" t="n">
-        <v>1.089</v>
+        <v>1.0523</v>
       </c>
       <c r="J127" t="n">
-        <v>27.225</v>
+        <v>26.3075</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.47</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0766</v>
+        <v>1.0379</v>
       </c>
       <c r="J128" t="n">
-        <v>26.915</v>
+        <v>25.9475</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.43</v>
       </c>
       <c r="I129" t="n">
-        <v>1.0236</v>
+        <v>0.9756</v>
       </c>
       <c r="J129" t="n">
-        <v>25.59</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8118</v>
+        <v>0.7743</v>
       </c>
       <c r="J130" t="n">
-        <v>20.295</v>
+        <v>19.3575</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.177</v>
+        <v>-0.1575</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.425</v>
+        <v>-3.9375</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3287</v>
+        <v>0.3129</v>
       </c>
       <c r="J132" t="n">
-        <v>7.5601</v>
+        <v>7.1967</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1535</v>
+        <v>-0.1725</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.5305</v>
+        <v>-3.9675</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2049</v>
+        <v>-0.2239</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.7127</v>
+        <v>-5.1497</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2709</v>
+        <v>-0.2893</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.2307</v>
+        <v>-6.6539</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5601</v>
+        <v>-0.5645</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.8823</v>
+        <v>-12.9835</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3323</v>
+        <v>1.3116</v>
       </c>
       <c r="J137" t="n">
-        <v>30.6429</v>
+        <v>30.1668</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.42</v>
       </c>
       <c r="I138" t="n">
-        <v>1.018</v>
+        <v>0.9671</v>
       </c>
       <c r="J138" t="n">
-        <v>23.414</v>
+        <v>22.2433</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9477</v>
+        <v>0.8944</v>
       </c>
       <c r="J139" t="n">
-        <v>21.7971</v>
+        <v>20.5712</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0641</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>1.4743</v>
+        <v>2.0677</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3646</v>
+        <v>-0.3397</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.3858</v>
+        <v>-7.8131</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7392</v>
+        <v>0.7328</v>
       </c>
       <c r="J142" t="n">
-        <v>18.48</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3042</v>
+        <v>0.3215</v>
       </c>
       <c r="J143" t="n">
-        <v>7.605</v>
+        <v>8.0375</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2927</v>
+        <v>0.3101</v>
       </c>
       <c r="J144" t="n">
-        <v>7.3175</v>
+        <v>7.7525</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1064</v>
+        <v>0.1242</v>
       </c>
       <c r="J145" t="n">
-        <v>2.66</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0849</v>
+        <v>-0.0893</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.1225</v>
+        <v>-2.2325</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5699</v>
+        <v>0.5551</v>
       </c>
       <c r="J147" t="n">
-        <v>14.2475</v>
+        <v>13.8775</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1339</v>
+        <v>0.1408</v>
       </c>
       <c r="J148" t="n">
-        <v>3.3475</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.21</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2425</v>
+        <v>-0.2573</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0625</v>
+        <v>-6.4325</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4049</v>
+        <v>-0.415</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.1225</v>
+        <v>-10.375</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.07</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3085</v>
+        <v>0.2834</v>
       </c>
       <c r="J152" t="n">
-        <v>6.787</v>
+        <v>6.2348</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0402</v>
+        <v>-0.0618</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.8844</v>
+        <v>-1.3596</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.7</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2983</v>
+        <v>-0.3182</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.5626</v>
+        <v>-7.0004</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.447</v>
+        <v>-0.4602</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.834</v>
+        <v>-10.1244</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6704</v>
+        <v>-0.6679</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.7488</v>
+        <v>-14.6938</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.92</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5881</v>
+        <v>1.5875</v>
       </c>
       <c r="J157" t="n">
-        <v>34.9382</v>
+        <v>34.925</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.59</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2066</v>
+        <v>1.1831</v>
       </c>
       <c r="J158" t="n">
-        <v>26.5452</v>
+        <v>26.0282</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0638</v>
+        <v>1.0259</v>
       </c>
       <c r="J159" t="n">
-        <v>23.4036</v>
+        <v>22.5698</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.86</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>18.92</v>
+        <v>18.0422</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.85</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5935</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.057</v>
+        <v>-11.9416</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5806</v>
       </c>
       <c r="J162" t="n">
-        <v>17.829</v>
+        <v>17.418</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4907</v>
+        <v>0.4857</v>
       </c>
       <c r="J163" t="n">
-        <v>14.721</v>
+        <v>14.571</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1926</v>
+        <v>0.2036</v>
       </c>
       <c r="J164" t="n">
-        <v>5.778</v>
+        <v>6.108</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1635</v>
+        <v>-0.175</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.905</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2161</v>
+        <v>-0.228</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.483</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.39</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0163</v>
+        <v>0.9554</v>
       </c>
       <c r="J167" t="n">
-        <v>30.489</v>
+        <v>28.662</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.428</v>
+        <v>0.4213</v>
       </c>
       <c r="J168" t="n">
-        <v>12.84</v>
+        <v>12.639</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.01</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0303</v>
+        <v>0.0429</v>
       </c>
       <c r="J169" t="n">
-        <v>0.909</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0245</v>
+        <v>-0.0168</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.735</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.379</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4869</v>
+        <v>0.4657</v>
       </c>
       <c r="J172" t="n">
-        <v>11.1987</v>
+        <v>10.7111</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1105</v>
+        <v>0.1056</v>
       </c>
       <c r="J173" t="n">
-        <v>2.5415</v>
+        <v>2.4288</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3161</v>
+        <v>-0.3319</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.2703</v>
+        <v>-7.6337</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3257</v>
+        <v>-0.3411</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.4911</v>
+        <v>-7.8453</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4103</v>
+        <v>-0.4223</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.4369</v>
+        <v>-9.712899999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3265</v>
+        <v>1.3065</v>
       </c>
       <c r="J177" t="n">
-        <v>30.5095</v>
+        <v>30.0495</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0284</v>
+        <v>0.98</v>
       </c>
       <c r="J178" t="n">
-        <v>23.6532</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8799</v>
+        <v>0.8337</v>
       </c>
       <c r="J179" t="n">
-        <v>20.2377</v>
+        <v>19.1751</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3868</v>
+        <v>0.3931</v>
       </c>
       <c r="J180" t="n">
-        <v>8.8964</v>
+        <v>9.0413</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2763</v>
+        <v>-0.2554</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.3549</v>
+        <v>-5.8742</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.68</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3348</v>
+        <v>1.3159</v>
       </c>
       <c r="J182" t="n">
-        <v>32.0352</v>
+        <v>31.5816</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.5</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1157</v>
+        <v>1.0816</v>
       </c>
       <c r="J183" t="n">
-        <v>26.7768</v>
+        <v>25.9584</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8556</v>
+        <v>0.8128</v>
       </c>
       <c r="J184" t="n">
-        <v>20.5344</v>
+        <v>19.5072</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.32</v>
       </c>
       <c r="I185" t="n">
-        <v>0.8133</v>
+        <v>0.7753</v>
       </c>
       <c r="J185" t="n">
-        <v>19.5192</v>
+        <v>18.6072</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7532</v>
+        <v>-0.6898</v>
       </c>
       <c r="J186" t="n">
-        <v>-18.0768</v>
+        <v>-16.5552</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.884</v>
+        <v>-2.2008</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.884</v>
+        <v>-2.2008</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.1696</v>
+        <v>-2.5008</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.196</v>
+        <v>-0.2124</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.704</v>
+        <v>-5.0976</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.196</v>
+        <v>-0.2124</v>
       </c>
       <c r="J191" t="n">
-        <v>-4.704</v>
+        <v>-5.0976</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3222</v>
+        <v>1.307</v>
       </c>
       <c r="J192" t="n">
-        <v>29.0884</v>
+        <v>28.754</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2639</v>
+        <v>1.2448</v>
       </c>
       <c r="J193" t="n">
-        <v>27.8058</v>
+        <v>27.3856</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.43</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0105</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>22.231</v>
+        <v>21.2124</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.8756</v>
       </c>
       <c r="J195" t="n">
-        <v>20.2818</v>
+        <v>19.2632</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2182</v>
+        <v>0.2449</v>
       </c>
       <c r="J196" t="n">
-        <v>4.8004</v>
+        <v>5.3878</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.84</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1507</v>
+        <v>-0.1751</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.3154</v>
+        <v>-3.8522</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.79</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2051</v>
+        <v>-0.2284</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.5122</v>
+        <v>-5.0248</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.64</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3483</v>
+        <v>-0.3675</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.6626</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.61</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.376</v>
+        <v>-0.3939</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.272</v>
+        <v>-8.665800000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.5</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4788</v>
+        <v>-0.4909</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.5336</v>
+        <v>-10.7998</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.22</v>
       </c>
       <c r="I202" t="n">
-        <v>0.499</v>
+        <v>0.485</v>
       </c>
       <c r="J202" t="n">
-        <v>13.473</v>
+        <v>13.095</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.326</v>
+        <v>0.3241</v>
       </c>
       <c r="J203" t="n">
-        <v>8.802</v>
+        <v>8.7507</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2112</v>
+        <v>-0.2264</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.7024</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2709</v>
+        <v>-0.2854</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.3143</v>
+        <v>-7.7058</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.75</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2806</v>
+        <v>-0.2949</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.5762</v>
+        <v>-7.9623</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5884</v>
+        <v>1.573</v>
       </c>
       <c r="J207" t="n">
-        <v>42.8868</v>
+        <v>42.471</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.31</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8371</v>
+        <v>0.7875</v>
       </c>
       <c r="J208" t="n">
-        <v>22.6017</v>
+        <v>21.2625</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.14</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4224</v>
+        <v>0.4176</v>
       </c>
       <c r="J209" t="n">
-        <v>11.4048</v>
+        <v>11.2752</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.92</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3279</v>
+        <v>-0.3139</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.853300000000001</v>
+        <v>-8.475300000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.4462</v>
+        <v>-1.2948</v>
       </c>
       <c r="J211" t="n">
-        <v>-39.0474</v>
+        <v>-34.9596</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I212" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="J212" t="n">
-        <v>29.575</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.06</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2245</v>
+        <v>0.2273</v>
       </c>
       <c r="J213" t="n">
-        <v>14.5925</v>
+        <v>14.7745</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0511</v>
+        <v>0.0572</v>
       </c>
       <c r="J214" t="n">
-        <v>3.3215</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.01</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0511</v>
+        <v>0.0572</v>
       </c>
       <c r="J215" t="n">
-        <v>3.3215</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4659</v>
+        <v>-0.4476</v>
       </c>
       <c r="J216" t="n">
-        <v>-30.2835</v>
+        <v>-29.094</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.488</v>
+        <v>0.4837</v>
       </c>
       <c r="J217" t="n">
-        <v>31.72</v>
+        <v>31.4405</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2113</v>
+        <v>0.2223</v>
       </c>
       <c r="J218" t="n">
-        <v>13.7345</v>
+        <v>14.4495</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1504</v>
+        <v>0.1621</v>
       </c>
       <c r="J219" t="n">
-        <v>9.776</v>
+        <v>10.5365</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0555</v>
+        <v>0.0659</v>
       </c>
       <c r="J220" t="n">
-        <v>3.6075</v>
+        <v>4.2835</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0575</v>
+        <v>-0.064</v>
       </c>
       <c r="J221" t="n">
-        <v>-3.7375</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.77</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4281</v>
+        <v>1.417</v>
       </c>
       <c r="J222" t="n">
-        <v>28.562</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.68</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3224</v>
+        <v>1.305</v>
       </c>
       <c r="J223" t="n">
-        <v>26.448</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8907</v>
+        <v>0.8454</v>
       </c>
       <c r="J224" t="n">
-        <v>17.814</v>
+        <v>16.908</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5239</v>
+        <v>0.5203</v>
       </c>
       <c r="J225" t="n">
-        <v>10.478</v>
+        <v>10.406</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4446</v>
+        <v>-0.4091</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.891999999999999</v>
+        <v>-8.182</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5625</v>
+        <v>0.5252</v>
       </c>
       <c r="J227" t="n">
-        <v>11.25</v>
+        <v>10.504</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1685</v>
+        <v>-0.189</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.37</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.62</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3788</v>
+        <v>-0.3945</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.576</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3882</v>
+        <v>-0.4034</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.764</v>
+        <v>-8.068</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.49</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5</v>
+        <v>-0.509</v>
       </c>
       <c r="J231" t="n">
-        <v>-10</v>
+        <v>-10.18</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2938</v>
+        <v>1.2667</v>
       </c>
       <c r="J232" t="n">
-        <v>36.2264</v>
+        <v>35.4676</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6309</v>
+        <v>0.6088</v>
       </c>
       <c r="J233" t="n">
-        <v>17.6652</v>
+        <v>17.0464</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.303</v>
+        <v>0.3106</v>
       </c>
       <c r="J234" t="n">
-        <v>8.484</v>
+        <v>8.6968</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1528</v>
+        <v>0.1698</v>
       </c>
       <c r="J235" t="n">
-        <v>4.2784</v>
+        <v>4.7544</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1031</v>
+        <v>-0.093</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.8868</v>
+        <v>-2.604</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.3</v>
       </c>
       <c r="I237" t="n">
-        <v>0.647</v>
+        <v>0.6194</v>
       </c>
       <c r="J237" t="n">
-        <v>18.116</v>
+        <v>17.3432</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2241</v>
+        <v>0.2263</v>
       </c>
       <c r="J238" t="n">
-        <v>6.2748</v>
+        <v>6.3364</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2105</v>
+        <v>-0.2259</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.894</v>
+        <v>-6.3252</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2206</v>
+        <v>-0.2359</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.1768</v>
+        <v>-6.6052</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3845</v>
+        <v>-0.3957</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.766</v>
+        <v>-11.0796</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2112/event_2112_evp_summary.xlsx
+++ b/database/event/2112/event_2112_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4722</v>
+        <v>6.5548</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7562</v>
+        <v>1.7786</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3221</v>
+        <v>2.3802</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4722</v>
+        <v>6.5548</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3564</v>
+        <v>2.447</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1158</v>
+        <v>4.1078</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8804</v>
+        <v>2.7446</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5554</v>
+        <v>1.541</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1158</v>
+        <v>4.1078</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>129</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6712</v>
+        <v>5.6488</v>
       </c>
       <c r="N2" t="n">
         <v>179</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9736</v>
+        <v>5.93</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6209</v>
+        <v>1.609</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0951</v>
+        <v>2.0956</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9736</v>
+        <v>5.93</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9279</v>
+        <v>2.9556</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0456</v>
+        <v>2.9744</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7662</v>
+        <v>4.6539</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5737</v>
+        <v>2.613</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0456</v>
+        <v>2.9744</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -575,7 +575,7 @@
         <v>129</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6193</v>
+        <v>5.587400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>179</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9893</v>
+        <v>4.8303</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3538</v>
+        <v>1.3106</v>
       </c>
       <c r="D4" t="n">
-        <v>1.647</v>
+        <v>1.5946</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9893</v>
+        <v>4.8303</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5947</v>
+        <v>3.507</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3946</v>
+        <v>1.3233</v>
       </c>
       <c r="H4" t="n">
-        <v>6.966</v>
+        <v>6.7242</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7616</v>
+        <v>3.7754</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3946</v>
+        <v>1.3233</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1562</v>
+        <v>5.0987</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4569</v>
+        <v>4.4229</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2093</v>
+        <v>1.2001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4047</v>
+        <v>1.4091</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4569</v>
+        <v>4.4229</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7349</v>
+        <v>2.7777</v>
       </c>
       <c r="G5" t="n">
-        <v>1.722</v>
+        <v>1.6452</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1293</v>
+        <v>3.986</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2298</v>
+        <v>2.238</v>
       </c>
       <c r="J5" t="n">
-        <v>1.722</v>
+        <v>1.6452</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>127</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9518</v>
+        <v>3.8832</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5992</v>
+        <v>3.7005</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9766</v>
+        <v>1.0041</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0142</v>
+        <v>1.08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5992</v>
+        <v>3.7005</v>
       </c>
       <c r="F6" t="n">
-        <v>2.393</v>
+        <v>2.4693</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2062</v>
+        <v>1.2312</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0013</v>
+        <v>2.8283</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6207</v>
+        <v>1.588</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2062</v>
+        <v>1.2312</v>
       </c>
       <c r="K6" t="n">
         <v>44</v>
@@ -713,7 +713,7 @@
         <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8269</v>
+        <v>2.8192</v>
       </c>
       <c r="N6" t="n">
         <v>171</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5899</v>
+        <v>3.4271</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9741</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.01</v>
+        <v>0.9554</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5899</v>
+        <v>3.4271</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7947</v>
+        <v>3.6543</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2048</v>
+        <v>-0.2272</v>
       </c>
       <c r="H7" t="n">
-        <v>7.626</v>
+        <v>7.2773</v>
       </c>
       <c r="I7" t="n">
-        <v>4.118</v>
+        <v>4.086</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2048</v>
+        <v>-0.2272</v>
       </c>
       <c r="K7" t="n">
         <v>142</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9132</v>
+        <v>3.8588</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,219 +768,219 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4709</v>
+        <v>3.3722</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9418</v>
+        <v>0.915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9558</v>
+        <v>0.9304</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4709</v>
+        <v>3.3722</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7408</v>
+        <v>1.5901</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2699</v>
+        <v>1.7821</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4483</v>
+        <v>1.5901</v>
       </c>
       <c r="I8" t="n">
-        <v>4.022</v>
+        <v>0.8928</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2699</v>
+        <v>1.7821</v>
       </c>
       <c r="K8" t="n">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7521</v>
+        <v>2.6749</v>
       </c>
       <c r="N8" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3691</v>
+        <v>3.3342</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9142</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9095</v>
+        <v>0.9131</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3691</v>
+        <v>3.3342</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6134</v>
+        <v>3.593</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7557</v>
+        <v>-0.2588</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6134</v>
+        <v>7.0471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8712</v>
+        <v>3.9567</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7557</v>
+        <v>-0.2588</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="L9" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6269</v>
+        <v>3.6979</v>
       </c>
       <c r="N9" t="n">
-        <v>179</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3098</v>
+        <v>3.2931</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8981</v>
+        <v>0.8935</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8825</v>
+        <v>0.8944</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3098</v>
+        <v>3.2931</v>
       </c>
       <c r="F10" t="n">
-        <v>1.581</v>
+        <v>2.9782</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7288</v>
+        <v>0.3149</v>
       </c>
       <c r="H10" t="n">
-        <v>1.581</v>
+        <v>4.739</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8537</v>
+        <v>2.6608</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7288</v>
+        <v>0.3149</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5825</v>
+        <v>2.9757</v>
       </c>
       <c r="N10" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2863</v>
+        <v>3.1931</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8917</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8718</v>
+        <v>0.8488</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2863</v>
+        <v>3.1931</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9544</v>
+        <v>2.861</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3319</v>
+        <v>0.3321</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8536</v>
+        <v>4.2989</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6209</v>
+        <v>2.4137</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3319</v>
+        <v>0.3321</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="L11" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9528</v>
+        <v>2.7458</v>
       </c>
       <c r="N11" t="n">
-        <v>171</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.265</v>
+        <v>3.1403</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8859</v>
+        <v>0.8521</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8621</v>
+        <v>0.8248</v>
       </c>
       <c r="E12" t="n">
-        <v>3.265</v>
+        <v>3.1403</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8572</v>
+        <v>3.2689</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4078</v>
+        <v>-0.1286</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5328</v>
+        <v>5.8302</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4477</v>
+        <v>3.2735</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4078</v>
+        <v>-0.1286</v>
       </c>
       <c r="K12" t="n">
         <v>196</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8555</v>
+        <v>3.1449</v>
       </c>
       <c r="N12" t="n">
         <v>273</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2371</v>
+        <v>3.0945</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8783</v>
+        <v>0.8397</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8494</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2371</v>
+        <v>3.0945</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3574</v>
+        <v>1.4038</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1203</v>
+        <v>1.6907</v>
       </c>
       <c r="H13" t="n">
-        <v>6.1831</v>
+        <v>1.4038</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3388</v>
+        <v>0.7882</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1203</v>
+        <v>1.6907</v>
       </c>
       <c r="K13" t="n">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2185</v>
+        <v>2.4789</v>
       </c>
       <c r="N13" t="n">
-        <v>273</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0957</v>
+        <v>2.9695</v>
       </c>
       <c r="C14" t="n">
-        <v>0.84</v>
+        <v>0.8057</v>
       </c>
       <c r="D14" t="n">
-        <v>0.785</v>
+        <v>0.747</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0957</v>
+        <v>2.9695</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9596</v>
+        <v>3.7919</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8639</v>
+        <v>-0.8224</v>
       </c>
       <c r="H14" t="n">
-        <v>8.1701</v>
+        <v>7.7938</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4118</v>
+        <v>4.376</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8639</v>
+        <v>-0.8224</v>
       </c>
       <c r="K14" t="n">
         <v>196</v>
@@ -1081,7 +1081,7 @@
         <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5479</v>
+        <v>3.5536</v>
       </c>
       <c r="N14" t="n">
         <v>273</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4438</v>
+        <v>2.4264</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6631</v>
+        <v>0.6584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4883</v>
+        <v>0.4996</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4438</v>
+        <v>2.4264</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8128</v>
+        <v>2.8491</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.369</v>
+        <v>-0.4227</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3864</v>
+        <v>4.254</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3686</v>
+        <v>2.3885</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.369</v>
+        <v>-0.4227</v>
       </c>
       <c r="K15" t="n">
         <v>142</v>
@@ -1127,7 +1127,7 @@
         <v>79</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9996</v>
+        <v>1.9658</v>
       </c>
       <c r="N15" t="n">
         <v>221</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1205</v>
+        <v>2.1552</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5754</v>
+        <v>0.5848</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3411</v>
+        <v>0.376</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1205</v>
+        <v>2.1552</v>
       </c>
       <c r="F16" t="n">
-        <v>2.952</v>
+        <v>2.9347</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8315</v>
+        <v>-0.7795</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8454</v>
+        <v>4.5755</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6165</v>
+        <v>2.569</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8315</v>
+        <v>-0.7795</v>
       </c>
       <c r="K16" t="n">
         <v>196</v>
@@ -1173,7 +1173,7 @@
         <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>1.785</v>
+        <v>1.7895</v>
       </c>
       <c r="N16" t="n">
         <v>273</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5312</v>
+        <v>1.4683</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4155</v>
+        <v>0.3984</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0728</v>
+        <v>0.0631</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5312</v>
+        <v>1.4683</v>
       </c>
       <c r="F17" t="n">
-        <v>1.936</v>
+        <v>-0.3067</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4048</v>
+        <v>1.775</v>
       </c>
       <c r="H17" t="n">
-        <v>1.936</v>
+        <v>-0.3067</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0454</v>
+        <v>-0.1722</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4048</v>
+        <v>1.775</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L17" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6406000000000001</v>
+        <v>1.6028</v>
       </c>
       <c r="N17" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4781</v>
+        <v>1.4184</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4011</v>
+        <v>0.3849</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0487</v>
+        <v>0.0404</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4781</v>
+        <v>1.4184</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3139</v>
+        <v>1.8012</v>
       </c>
       <c r="G18" t="n">
-        <v>1.792</v>
+        <v>-0.3828</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3139</v>
+        <v>1.8012</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1695</v>
+        <v>1.0113</v>
       </c>
       <c r="J18" t="n">
-        <v>1.792</v>
+        <v>-0.3828</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6225</v>
+        <v>0.6285000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2678</v>
+        <v>1.2879</v>
       </c>
       <c r="C19" t="n">
-        <v>0.344</v>
+        <v>0.3495</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0471</v>
+        <v>-0.0191</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2678</v>
+        <v>1.2879</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2454</v>
+        <v>1.2811</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0224</v>
+        <v>0.0068</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2454</v>
+        <v>1.2811</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6725</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0224</v>
+        <v>0.0068</v>
       </c>
       <c r="K19" t="n">
         <v>44</v>
@@ -1311,7 +1311,7 @@
         <v>127</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6949</v>
+        <v>0.7261000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>171</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3196</v>
+        <v>0.2755</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0881</v>
+        <v>-0.1432</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1777</v>
+        <v>1.0155</v>
       </c>
       <c r="N20" t="n">
         <v>81</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2355</v>
+        <v>0.2178</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.229</v>
+        <v>-0.2401</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8681</v>
+        <v>0.8028</v>
       </c>
       <c r="N21" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1947</v>
+        <v>0.2071</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2976</v>
+        <v>-0.258</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7174</v>
+        <v>0.7634</v>
       </c>
       <c r="N22" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1946</v>
+        <v>0.1623</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2978</v>
+        <v>-0.3333</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7171</v>
+        <v>0.5982</v>
       </c>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1722</v>
+        <v>0.1549</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3353</v>
+        <v>-0.3457</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6347</v>
+        <v>0.571</v>
       </c>
       <c r="N24" t="n">
         <v>96</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1566</v>
+        <v>0.1461</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3614</v>
+        <v>-0.3605</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5773</v>
+        <v>0.5385</v>
       </c>
       <c r="N25" t="n">
         <v>96</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1388</v>
+        <v>0.1122</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3914</v>
+        <v>-0.4174</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5114</v>
+        <v>0.4135</v>
       </c>
       <c r="N26" t="n">
         <v>165</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0987</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4586</v>
+        <v>-0.4591</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3637</v>
+        <v>0.3221</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0199</v>
+        <v>0.0072</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5908</v>
+        <v>-0.5937</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0733</v>
+        <v>0.0265</v>
       </c>
       <c r="N28" t="n">
         <v>81</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4112</v>
+        <v>-0.3839</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1116</v>
+        <v>-0.1042</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8114</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4112</v>
+        <v>-0.3839</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4112</v>
+        <v>-0.654</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.2701</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4112</v>
+        <v>-0.654</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4112</v>
+        <v>-0.3672</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2701</v>
       </c>
       <c r="K29" t="n">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4112</v>
+        <v>-0.09710000000000002</v>
       </c>
       <c r="N29" t="n">
-        <v>90</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1241</v>
+        <v>-0.1216</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8324</v>
+        <v>-0.8099</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4573</v>
+        <v>-0.4481</v>
       </c>
       <c r="N30" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4889</v>
+        <v>-0.4875</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1327</v>
+        <v>-0.1323</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8468</v>
+        <v>-0.8279</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4889</v>
+        <v>-0.4875</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7691</v>
+        <v>-0.4875</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2802</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7691</v>
+        <v>-0.4875</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4153</v>
+        <v>-0.4875</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2802</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1351</v>
+        <v>-0.4875</v>
       </c>
       <c r="N31" t="n">
-        <v>273</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1462</v>
+        <v>-0.1488</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8556</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="N32" t="n">
         <v>165</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1564</v>
+        <v>-0.1488</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8556</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5764</v>
+        <v>-0.5483</v>
       </c>
       <c r="N33" t="n">
         <v>96</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>hooch</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2075</v>
+        <v>-0.2005</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9423</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="N34" t="n">
-        <v>165</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hooch</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2157</v>
+        <v>-0.2051</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9861</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.795</v>
+        <v>-0.7559</v>
       </c>
       <c r="N35" t="n">
-        <v>81</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9656</v>
+        <v>-0.9264</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.262</v>
+        <v>-0.2514</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0638</v>
+        <v>-1.0278</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9656</v>
+        <v>-0.9264</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1987</v>
+        <v>-0.9264</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7669</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1987</v>
+        <v>-0.9264</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1073</v>
+        <v>-0.9264</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7669</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="L36" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8742000000000001</v>
+        <v>-0.9264</v>
       </c>
       <c r="N36" t="n">
-        <v>221</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9412</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2668</v>
+        <v>-0.2554</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0719</v>
+        <v>-1.0345</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9412</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.223</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.223</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.1252</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.8433999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>90</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2694</v>
+        <v>-0.2583</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0762</v>
+        <v>-1.0394</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.993</v>
+        <v>-0.9518</v>
       </c>
       <c r="N38" t="n">
         <v>81</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3507</v>
+        <v>-0.3378</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2126</v>
+        <v>-1.173</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2925</v>
+        <v>-1.2451</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3853</v>
+        <v>-0.4091</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2706</v>
+        <v>-1.2927</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4199</v>
+        <v>-1.5079</v>
       </c>
       <c r="N40" t="n">
         <v>90</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6592</v>
+        <v>-0.6637</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7302</v>
+        <v>-1.7201</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4295</v>
+        <v>-2.446</v>
       </c>
       <c r="N41" t="n">
         <v>96</v>
@@ -2429,10 +2429,10 @@
         <v>1.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4421</v>
+        <v>0.3931</v>
       </c>
       <c r="J2" t="n">
-        <v>11.0525</v>
+        <v>9.827500000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.081</v>
+        <v>-0.0682</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.025</v>
+        <v>-1.705</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2726</v>
+        <v>-0.2548</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.815</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.401</v>
+        <v>-0.3895</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.025</v>
+        <v>-9.737500000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.55</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4629</v>
+        <v>-0.4576</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.5725</v>
+        <v>-11.44</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4809</v>
+        <v>1.5156</v>
       </c>
       <c r="J7" t="n">
-        <v>37.0225</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.31</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7653</v>
+        <v>0.7407</v>
       </c>
       <c r="J8" t="n">
-        <v>19.1325</v>
+        <v>18.5175</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6651</v>
+        <v>0.6363</v>
       </c>
       <c r="J9" t="n">
-        <v>16.6275</v>
+        <v>15.9075</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4032</v>
+        <v>0.3701</v>
       </c>
       <c r="J10" t="n">
-        <v>10.08</v>
+        <v>9.2525</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6095</v>
+        <v>-0.576</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.2375</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.03</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1174</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.935</v>
+        <v>2.1875</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1174</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.935</v>
+        <v>2.1875</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1169</v>
+        <v>-0.1008</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.9225</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1926</v>
+        <v>-0.1731</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.815</v>
+        <v>-4.3275</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.68</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3568</v>
+        <v>-0.3421</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.92</v>
+        <v>-8.5525</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.164</v>
+        <v>1.1746</v>
       </c>
       <c r="J17" t="n">
-        <v>29.1</v>
+        <v>29.365</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0346</v>
+        <v>1.0309</v>
       </c>
       <c r="J18" t="n">
-        <v>25.865</v>
+        <v>25.7725</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5621</v>
+        <v>0.5305</v>
       </c>
       <c r="J19" t="n">
-        <v>14.0525</v>
+        <v>13.2625</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4032</v>
+        <v>0.3701</v>
       </c>
       <c r="J20" t="n">
-        <v>10.08</v>
+        <v>9.2525</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3877</v>
+        <v>-0.3477</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.692500000000001</v>
+        <v>-8.692500000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.63</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0855</v>
+        <v>1.078</v>
       </c>
       <c r="J22" t="n">
-        <v>21.71</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0603</v>
+        <v>1.0522</v>
       </c>
       <c r="J23" t="n">
-        <v>21.206</v>
+        <v>21.044</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.48</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8939</v>
+        <v>0.8844</v>
       </c>
       <c r="J24" t="n">
-        <v>17.878</v>
+        <v>17.688</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7482</v>
+        <v>0.7408</v>
       </c>
       <c r="J25" t="n">
-        <v>14.964</v>
+        <v>14.816</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3233</v>
+        <v>0.2905</v>
       </c>
       <c r="J26" t="n">
-        <v>6.466</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0471</v>
+        <v>0.0624</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.75</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2684</v>
+        <v>-0.2548</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.368</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3587</v>
+        <v>-0.3466</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.174</v>
+        <v>-6.932</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.878</v>
+        <v>-7.662</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5956</v>
+        <v>-0.6073</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.912</v>
+        <v>-12.146</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4385</v>
+        <v>0.4437</v>
       </c>
       <c r="J32" t="n">
-        <v>13.155</v>
+        <v>13.311</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.256</v>
+        <v>0.2413</v>
       </c>
       <c r="J33" t="n">
-        <v>7.68</v>
+        <v>7.239</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0431</v>
+        <v>-0.0327</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.293</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2124</v>
+        <v>-0.1918</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.372</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2628</v>
+        <v>-0.2433</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.884</v>
+        <v>-7.299</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4961</v>
+        <v>0.4474</v>
       </c>
       <c r="J37" t="n">
-        <v>14.883</v>
+        <v>13.422</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3805</v>
+        <v>0.3185</v>
       </c>
       <c r="J38" t="n">
-        <v>11.415</v>
+        <v>9.555</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0473</v>
+        <v>0.0329</v>
       </c>
       <c r="J39" t="n">
-        <v>1.419</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1193</v>
+        <v>-0.1007</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.579</v>
+        <v>-3.021</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1774</v>
+        <v>-0.157</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.322</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9351</v>
+        <v>0.9227</v>
       </c>
       <c r="J42" t="n">
-        <v>27.1179</v>
+        <v>26.7583</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6491</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18.8239</v>
+        <v>18.4034</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4667</v>
+        <v>0.4355</v>
       </c>
       <c r="J44" t="n">
-        <v>13.5343</v>
+        <v>12.6295</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7353</v>
+        <v>-0.7058</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.3237</v>
+        <v>-20.4682</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8429</v>
+        <v>-0.823</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.4441</v>
+        <v>-23.867</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.59</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8514</v>
+        <v>0.8135</v>
       </c>
       <c r="J47" t="n">
-        <v>24.6906</v>
+        <v>23.5915</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3665</v>
+        <v>0.3129</v>
       </c>
       <c r="J48" t="n">
-        <v>10.6285</v>
+        <v>9.0741</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0488</v>
+        <v>-0.0369</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.4152</v>
+        <v>-1.0701</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1539</v>
+        <v>-0.1339</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.4631</v>
+        <v>-3.8831</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2889</v>
+        <v>-0.2709</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.3781</v>
+        <v>-7.8561</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.63</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1114</v>
+        <v>1.1031</v>
       </c>
       <c r="J52" t="n">
-        <v>27.785</v>
+        <v>27.5775</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8306</v>
+        <v>0.8167</v>
       </c>
       <c r="J53" t="n">
-        <v>20.765</v>
+        <v>20.4175</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6179</v>
+        <v>0.6103</v>
       </c>
       <c r="J54" t="n">
-        <v>15.4475</v>
+        <v>15.2575</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I55" t="n">
-        <v>0.269</v>
+        <v>0.238</v>
       </c>
       <c r="J55" t="n">
-        <v>6.725</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1226</v>
+        <v>0.0988</v>
       </c>
       <c r="J56" t="n">
-        <v>3.065</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2926</v>
+        <v>0.2498</v>
       </c>
       <c r="J57" t="n">
-        <v>7.315</v>
+        <v>6.245</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.103</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.575</v>
+        <v>-2.2225</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3168</v>
+        <v>-0.3006</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.92</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.64</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3805</v>
+        <v>-0.3676</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.512499999999999</v>
+        <v>-9.19</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4429</v>
+        <v>-0.4353</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.0725</v>
+        <v>-10.8825</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4322</v>
+        <v>0.4377</v>
       </c>
       <c r="J62" t="n">
-        <v>11.2372</v>
+        <v>11.3802</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.1216</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.88</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1631</v>
+        <v>-0.1438</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.2406</v>
+        <v>-3.7388</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2357</v>
+        <v>-0.2157</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.1282</v>
+        <v>-5.6082</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3036</v>
+        <v>-0.2857</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.8936</v>
+        <v>-7.4282</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6434</v>
+        <v>0.6026</v>
       </c>
       <c r="J67" t="n">
-        <v>16.7284</v>
+        <v>15.6676</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.45</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5385</v>
+        <v>0.5008</v>
       </c>
       <c r="J68" t="n">
-        <v>14.001</v>
+        <v>13.0208</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2631</v>
+        <v>0.2147</v>
       </c>
       <c r="J69" t="n">
-        <v>6.8406</v>
+        <v>5.5822</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1151</v>
+        <v>-0.0974</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.9926</v>
+        <v>-2.5324</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.218</v>
+        <v>-0.1986</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.668</v>
+        <v>-5.1636</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.259</v>
+        <v>1.2586</v>
       </c>
       <c r="J72" t="n">
-        <v>32.734</v>
+        <v>32.7236</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8073</v>
+        <v>0.7964</v>
       </c>
       <c r="J73" t="n">
-        <v>20.9898</v>
+        <v>20.7064</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.39</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7803</v>
+        <v>0.77</v>
       </c>
       <c r="J74" t="n">
-        <v>20.2878</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4286</v>
+        <v>0.3993</v>
       </c>
       <c r="J75" t="n">
-        <v>11.1436</v>
+        <v>10.3818</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4065</v>
+        <v>0.3753</v>
       </c>
       <c r="J76" t="n">
-        <v>10.569</v>
+        <v>9.7578</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1479</v>
+        <v>-0.1324</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.8454</v>
+        <v>-3.4424</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.7652</v>
+        <v>-6.3336</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.75</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2783</v>
+        <v>-0.2618</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.2358</v>
+        <v>-6.8068</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2967</v>
+        <v>-0.2803</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.7142</v>
+        <v>-7.2878</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3059</v>
+        <v>-0.2897</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9534</v>
+        <v>-7.5322</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0901</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>-2.0723</v>
+        <v>-1.7227</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.77</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2551</v>
+        <v>-0.2402</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.8673</v>
+        <v>-5.5246</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.65</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3635</v>
+        <v>-0.3504</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.3605</v>
+        <v>-8.059200000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3635</v>
+        <v>-0.3504</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.3605</v>
+        <v>-8.059200000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4081</v>
+        <v>-0.3975</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.3863</v>
+        <v>-9.1425</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1199</v>
+        <v>1.1332</v>
       </c>
       <c r="J87" t="n">
-        <v>25.7577</v>
+        <v>26.0636</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0801</v>
+        <v>1.0913</v>
       </c>
       <c r="J88" t="n">
-        <v>24.8423</v>
+        <v>25.0999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.35</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8306</v>
+        <v>0.8145</v>
       </c>
       <c r="J89" t="n">
-        <v>19.1038</v>
+        <v>18.7335</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4827</v>
+        <v>0.4522</v>
       </c>
       <c r="J90" t="n">
-        <v>11.1021</v>
+        <v>10.4006</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3144</v>
+        <v>0.2826</v>
       </c>
       <c r="J91" t="n">
-        <v>7.2312</v>
+        <v>6.4998</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4114</v>
+        <v>0.357</v>
       </c>
       <c r="J92" t="n">
-        <v>9.050800000000001</v>
+        <v>7.854</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2573</v>
+        <v>0.2109</v>
       </c>
       <c r="J93" t="n">
-        <v>5.6606</v>
+        <v>4.6398</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.06</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1927</v>
+        <v>0.1526</v>
       </c>
       <c r="J94" t="n">
-        <v>4.2394</v>
+        <v>3.3572</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.63</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4007</v>
+        <v>-0.3896</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.8154</v>
+        <v>-8.571199999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.5</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5142</v>
+        <v>-0.5164</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.3124</v>
+        <v>-11.3608</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7996</v>
+        <v>0.7786</v>
       </c>
       <c r="J97" t="n">
-        <v>17.5912</v>
+        <v>17.1292</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7802</v>
+        <v>0.7581</v>
       </c>
       <c r="J98" t="n">
-        <v>17.1644</v>
+        <v>16.6782</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.3</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7411</v>
+        <v>0.7171</v>
       </c>
       <c r="J99" t="n">
-        <v>16.3042</v>
+        <v>15.7762</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.25</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6421</v>
+        <v>0.6142</v>
       </c>
       <c r="J100" t="n">
-        <v>14.1262</v>
+        <v>13.5124</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.18</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4915</v>
+        <v>0.4599</v>
       </c>
       <c r="J101" t="n">
-        <v>10.813</v>
+        <v>10.1178</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.03</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1139</v>
+        <v>0.0844</v>
       </c>
       <c r="J102" t="n">
-        <v>2.7336</v>
+        <v>2.0256</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.02</v>
       </c>
       <c r="I103" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="J103" t="n">
-        <v>2.076</v>
+        <v>1.4904</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1403</v>
+        <v>-0.1223</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.3672</v>
+        <v>-2.9352</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.3928</v>
+        <v>-4.9128</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.82</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.3928</v>
+        <v>-4.9128</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1917</v>
+        <v>1.2068</v>
       </c>
       <c r="J107" t="n">
-        <v>28.6008</v>
+        <v>28.9632</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5476</v>
+        <v>0.5123</v>
       </c>
       <c r="J108" t="n">
-        <v>13.1424</v>
+        <v>12.2952</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.19</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5259</v>
+        <v>0.4903</v>
       </c>
       <c r="J109" t="n">
-        <v>12.6216</v>
+        <v>11.7672</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1736</v>
+        <v>0.1471</v>
       </c>
       <c r="J110" t="n">
-        <v>4.1664</v>
+        <v>3.5304</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4281</v>
+        <v>-0.3867</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.2744</v>
+        <v>-9.280799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4383</v>
+        <v>0.3729</v>
       </c>
       <c r="J112" t="n">
-        <v>12.7107</v>
+        <v>10.8141</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.11</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1984</v>
+        <v>0.1544</v>
       </c>
       <c r="J113" t="n">
-        <v>5.7536</v>
+        <v>4.4776</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1393</v>
+        <v>0.1046</v>
       </c>
       <c r="J114" t="n">
-        <v>4.0397</v>
+        <v>3.0334</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.204</v>
+        <v>-0.1833</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.916</v>
+        <v>-5.3157</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.245</v>
+        <v>-0.2249</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.105</v>
+        <v>-6.5221</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6829</v>
+        <v>0.7202</v>
       </c>
       <c r="J117" t="n">
-        <v>19.8041</v>
+        <v>20.8858</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3895</v>
+        <v>0.3874</v>
       </c>
       <c r="J118" t="n">
-        <v>11.2955</v>
+        <v>11.2346</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.23</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3531</v>
+        <v>0.3481</v>
       </c>
       <c r="J119" t="n">
-        <v>10.2399</v>
+        <v>10.0949</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0726</v>
+        <v>-0.0584</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.1054</v>
+        <v>-1.6936</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1009</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.9261</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.03</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1612</v>
+        <v>0.1333</v>
       </c>
       <c r="J122" t="n">
-        <v>4.03</v>
+        <v>3.3325</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.76</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2686</v>
+        <v>-0.2524</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.715</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.73</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2958</v>
+        <v>-0.2797</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.395</v>
+        <v>-6.9925</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3413</v>
+        <v>-0.3265</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.532500000000001</v>
+        <v>-8.1625</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4133</v>
+        <v>-0.4029</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3325</v>
+        <v>-10.0725</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.48</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0523</v>
+        <v>1.0605</v>
       </c>
       <c r="J127" t="n">
-        <v>26.3075</v>
+        <v>26.5125</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.47</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0379</v>
+        <v>1.0443</v>
       </c>
       <c r="J128" t="n">
-        <v>25.9475</v>
+        <v>26.1075</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.43</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9756</v>
+        <v>0.9726</v>
       </c>
       <c r="J129" t="n">
-        <v>24.39</v>
+        <v>24.315</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I130" t="n">
-        <v>0.7743</v>
+        <v>0.755</v>
       </c>
       <c r="J130" t="n">
-        <v>19.3575</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1575</v>
+        <v>-0.1325</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.9375</v>
+        <v>-3.3125</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3129</v>
+        <v>0.2689</v>
       </c>
       <c r="J132" t="n">
-        <v>7.1967</v>
+        <v>6.1847</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1725</v>
+        <v>-0.1564</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.9675</v>
+        <v>-3.5972</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2239</v>
+        <v>-0.207</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.1497</v>
+        <v>-4.761</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2893</v>
+        <v>-0.2723</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.6539</v>
+        <v>-6.2629</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5645</v>
+        <v>-0.5728</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.9835</v>
+        <v>-13.1744</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3116</v>
+        <v>1.3316</v>
       </c>
       <c r="J137" t="n">
-        <v>30.1668</v>
+        <v>30.6268</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.42</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9671</v>
+        <v>0.9608</v>
       </c>
       <c r="J138" t="n">
-        <v>22.2433</v>
+        <v>22.0984</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8944</v>
+        <v>0.8799</v>
       </c>
       <c r="J139" t="n">
-        <v>20.5712</v>
+        <v>20.2377</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="J140" t="n">
-        <v>2.0677</v>
+        <v>1.5916</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3397</v>
+        <v>-0.3014</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.8131</v>
+        <v>-6.9322</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7328</v>
+        <v>0.661</v>
       </c>
       <c r="J142" t="n">
-        <v>18.32</v>
+        <v>16.525</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3215</v>
+        <v>0.2671</v>
       </c>
       <c r="J143" t="n">
-        <v>8.0375</v>
+        <v>6.6775</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3101</v>
+        <v>0.2568</v>
       </c>
       <c r="J144" t="n">
-        <v>7.7525</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1242</v>
+        <v>0.095</v>
       </c>
       <c r="J145" t="n">
-        <v>3.105</v>
+        <v>2.375</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0893</v>
+        <v>-0.0737</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.2325</v>
+        <v>-1.8425</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5551</v>
+        <v>0.5763</v>
       </c>
       <c r="J147" t="n">
-        <v>13.8775</v>
+        <v>14.4075</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1408</v>
+        <v>0.1236</v>
       </c>
       <c r="J148" t="n">
-        <v>3.52</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.56</v>
+        <v>-3.0925</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2573</v>
+        <v>-0.2375</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.4325</v>
+        <v>-5.9375</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.415</v>
+        <v>-0.4057</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.375</v>
+        <v>-10.1425</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.07</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2834</v>
+        <v>0.2511</v>
       </c>
       <c r="J152" t="n">
-        <v>6.2348</v>
+        <v>5.5242</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0618</v>
+        <v>-0.047</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.3596</v>
+        <v>-1.034</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.7</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3182</v>
+        <v>-0.3041</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.0004</v>
+        <v>-6.6902</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4602</v>
+        <v>-0.4541</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.1244</v>
+        <v>-9.9902</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6679</v>
+        <v>-0.6934</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.6938</v>
+        <v>-15.2548</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.92</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5875</v>
+        <v>1.6256</v>
       </c>
       <c r="J157" t="n">
-        <v>34.925</v>
+        <v>35.7632</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.59</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1831</v>
+        <v>1.1999</v>
       </c>
       <c r="J158" t="n">
-        <v>26.0282</v>
+        <v>26.3978</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0259</v>
+        <v>1.0346</v>
       </c>
       <c r="J159" t="n">
-        <v>22.5698</v>
+        <v>22.7612</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8081</v>
       </c>
       <c r="J160" t="n">
-        <v>18.0422</v>
+        <v>17.7782</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.85</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5118</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.9416</v>
+        <v>-11.2596</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5806</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>17.418</v>
+        <v>15.621</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4857</v>
+        <v>0.4269</v>
       </c>
       <c r="J163" t="n">
-        <v>14.571</v>
+        <v>12.807</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2036</v>
+        <v>0.1641</v>
       </c>
       <c r="J164" t="n">
-        <v>6.108</v>
+        <v>4.923</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.175</v>
+        <v>-0.1545</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.25</v>
+        <v>-4.635</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.228</v>
+        <v>-0.2077</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.84</v>
+        <v>-6.231</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.39</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9554</v>
+        <v>0.9445</v>
       </c>
       <c r="J167" t="n">
-        <v>28.662</v>
+        <v>28.335</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4213</v>
+        <v>0.3821</v>
       </c>
       <c r="J168" t="n">
-        <v>12.639</v>
+        <v>11.463</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.01</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0429</v>
+        <v>0.032</v>
       </c>
       <c r="J169" t="n">
-        <v>1.287</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0168</v>
+        <v>-0.0121</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.504</v>
+        <v>-0.363</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.295</v>
+        <v>-1.686</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4657</v>
+        <v>0.4137</v>
       </c>
       <c r="J172" t="n">
-        <v>10.7111</v>
+        <v>9.5151</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.02</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1056</v>
+        <v>0.0799</v>
       </c>
       <c r="J173" t="n">
-        <v>2.4288</v>
+        <v>1.8377</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3319</v>
+        <v>-0.3157</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.6337</v>
+        <v>-7.2611</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3411</v>
+        <v>-0.3254</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.8453</v>
+        <v>-7.4842</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4223</v>
+        <v>-0.4129</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.712899999999999</v>
+        <v>-9.496700000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3065</v>
+        <v>1.3261</v>
       </c>
       <c r="J177" t="n">
-        <v>30.0495</v>
+        <v>30.5003</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>0.98</v>
+        <v>0.9765</v>
       </c>
       <c r="J178" t="n">
-        <v>22.54</v>
+        <v>22.4595</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8337</v>
+        <v>0.8163</v>
       </c>
       <c r="J179" t="n">
-        <v>19.1751</v>
+        <v>18.7749</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3931</v>
+        <v>0.3611</v>
       </c>
       <c r="J180" t="n">
-        <v>9.0413</v>
+        <v>8.305300000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2554</v>
+        <v>-0.221</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.8742</v>
+        <v>-5.083</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.68</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3159</v>
+        <v>1.336</v>
       </c>
       <c r="J182" t="n">
-        <v>31.5816</v>
+        <v>32.064</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.5</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0816</v>
+        <v>1.0927</v>
       </c>
       <c r="J183" t="n">
-        <v>25.9584</v>
+        <v>26.2248</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8128</v>
+        <v>0.7951</v>
       </c>
       <c r="J184" t="n">
-        <v>19.5072</v>
+        <v>19.0824</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.32</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7753</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>18.6072</v>
+        <v>18.132</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6898</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.5552</v>
+        <v>-15.9312</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.2008</v>
+        <v>-1.8648</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.2008</v>
+        <v>-1.8648</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1042</v>
+        <v>-0.0892</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.5008</v>
+        <v>-2.1408</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2124</v>
+        <v>-0.1927</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.0976</v>
+        <v>-4.6248</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2124</v>
+        <v>-0.1927</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.0976</v>
+        <v>-4.6248</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.307</v>
+        <v>1.3278</v>
       </c>
       <c r="J192" t="n">
-        <v>28.754</v>
+        <v>29.2116</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2448</v>
+        <v>1.2633</v>
       </c>
       <c r="J193" t="n">
-        <v>27.3856</v>
+        <v>27.7926</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.43</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9649</v>
       </c>
       <c r="J194" t="n">
-        <v>21.2124</v>
+        <v>21.2278</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8756</v>
+        <v>0.8677</v>
       </c>
       <c r="J195" t="n">
-        <v>19.2632</v>
+        <v>19.0894</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2449</v>
+        <v>0.2124</v>
       </c>
       <c r="J196" t="n">
-        <v>5.3878</v>
+        <v>4.6728</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.84</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1751</v>
+        <v>-0.1591</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.8522</v>
+        <v>-3.5002</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.79</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2284</v>
+        <v>-0.2137</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.0248</v>
+        <v>-4.7014</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.64</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3675</v>
+        <v>-0.3556</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.8232</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.61</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.665800000000001</v>
+        <v>-8.4282</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.5</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4909</v>
+        <v>-0.488</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.7998</v>
+        <v>-10.736</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.22</v>
       </c>
       <c r="I202" t="n">
-        <v>0.485</v>
+        <v>0.4276</v>
       </c>
       <c r="J202" t="n">
-        <v>13.095</v>
+        <v>11.5452</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3241</v>
+        <v>0.272</v>
       </c>
       <c r="J203" t="n">
-        <v>8.7507</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2264</v>
+        <v>-0.2062</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.1128</v>
+        <v>-5.5674</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2854</v>
+        <v>-0.2666</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.7058</v>
+        <v>-7.1982</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.75</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2949</v>
+        <v>-0.2766</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.9623</v>
+        <v>-7.4682</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.84</v>
       </c>
       <c r="I207" t="n">
-        <v>1.573</v>
+        <v>1.6205</v>
       </c>
       <c r="J207" t="n">
-        <v>42.471</v>
+        <v>43.7535</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.31</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7875</v>
+        <v>0.7605</v>
       </c>
       <c r="J208" t="n">
-        <v>21.2625</v>
+        <v>20.5335</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.14</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4176</v>
+        <v>0.38</v>
       </c>
       <c r="J209" t="n">
-        <v>11.2752</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.92</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3139</v>
+        <v>-0.2728</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.475300000000001</v>
+        <v>-7.3656</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.2948</v>
+        <v>-1.3394</v>
       </c>
       <c r="J211" t="n">
-        <v>-34.9596</v>
+        <v>-36.1638</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.14</v>
       </c>
       <c r="I212" t="n">
-        <v>0.44</v>
+        <v>0.3974</v>
       </c>
       <c r="J212" t="n">
-        <v>28.6</v>
+        <v>25.831</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.06</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2273</v>
+        <v>0.1914</v>
       </c>
       <c r="J213" t="n">
-        <v>14.7745</v>
+        <v>12.441</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0572</v>
+        <v>0.0422</v>
       </c>
       <c r="J214" t="n">
-        <v>3.718</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.01</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0572</v>
+        <v>0.0422</v>
       </c>
       <c r="J215" t="n">
-        <v>3.718</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4476</v>
+        <v>-0.4046</v>
       </c>
       <c r="J216" t="n">
-        <v>-29.094</v>
+        <v>-26.299</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4837</v>
+        <v>0.425</v>
       </c>
       <c r="J217" t="n">
-        <v>31.4405</v>
+        <v>27.625</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2223</v>
+        <v>0.181</v>
       </c>
       <c r="J218" t="n">
-        <v>14.4495</v>
+        <v>11.765</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1621</v>
+        <v>0.1284</v>
       </c>
       <c r="J219" t="n">
-        <v>10.5365</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.02</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0659</v>
+        <v>0.0484</v>
       </c>
       <c r="J220" t="n">
-        <v>4.2835</v>
+        <v>3.146</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.064</v>
+        <v>-0.0501</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.16</v>
+        <v>-3.2565</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.77</v>
       </c>
       <c r="I222" t="n">
-        <v>1.417</v>
+        <v>1.4429</v>
       </c>
       <c r="J222" t="n">
-        <v>28.34</v>
+        <v>28.858</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.68</v>
       </c>
       <c r="I223" t="n">
-        <v>1.305</v>
+        <v>1.3248</v>
       </c>
       <c r="J223" t="n">
-        <v>26.1</v>
+        <v>26.496</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.36</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8454</v>
+        <v>0.8325</v>
       </c>
       <c r="J224" t="n">
-        <v>16.908</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5203</v>
+        <v>0.4916</v>
       </c>
       <c r="J225" t="n">
-        <v>10.406</v>
+        <v>9.832000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4091</v>
+        <v>-0.3734</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.182</v>
+        <v>-7.468</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5252</v>
+        <v>0.4844</v>
       </c>
       <c r="J227" t="n">
-        <v>10.504</v>
+        <v>9.688000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.189</v>
+        <v>-0.1732</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.78</v>
+        <v>-3.464</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.62</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3945</v>
+        <v>-0.3827</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.89</v>
+        <v>-7.654</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4034</v>
+        <v>-0.3922</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.068</v>
+        <v>-7.844</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.49</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.509</v>
+        <v>-0.5088</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.18</v>
+        <v>-10.176</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2667</v>
+        <v>1.2852</v>
       </c>
       <c r="J232" t="n">
-        <v>35.4676</v>
+        <v>35.9856</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6088</v>
+        <v>0.5758</v>
       </c>
       <c r="J233" t="n">
-        <v>17.0464</v>
+        <v>16.1224</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3106</v>
+        <v>0.2777</v>
       </c>
       <c r="J234" t="n">
-        <v>8.6968</v>
+        <v>7.7756</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1698</v>
+        <v>0.1436</v>
       </c>
       <c r="J235" t="n">
-        <v>4.7544</v>
+        <v>4.0208</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.99</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.093</v>
+        <v>-0.0721</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.604</v>
+        <v>-2.0188</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.3</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6194</v>
+        <v>0.5637</v>
       </c>
       <c r="J237" t="n">
-        <v>17.3432</v>
+        <v>15.7836</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2263</v>
+        <v>0.182</v>
       </c>
       <c r="J238" t="n">
-        <v>6.3364</v>
+        <v>5.096</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.82</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2259</v>
+        <v>-0.2057</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.3252</v>
+        <v>-5.7596</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2359</v>
+        <v>-0.2158</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.6052</v>
+        <v>-6.0424</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3957</v>
+        <v>-0.3844</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.0796</v>
+        <v>-10.7632</v>
       </c>
     </row>
   </sheetData>
